--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-09-2025.xlsx
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
+	GetHandleVerifier [0x0x7ff73ab91f10+80288]
+	(No symbol) [0x0x7ff73a9102fa]
+	(No symbol) [0x0x7ff73a967cd7]
+	(No symbol) [0x0x7ff73a967f9c]
+	(No symbol) [0x0x7ff73a9bba87]
+	(No symbol) [0x0x7ff73a9903bf]
+	(No symbol) [0x0x7ff73a9b87fb]
+	(No symbol) [0x0x7ff73a990153]
+	(No symbol) [0x0x7ff73a958b02]
+	(No symbol) [0x0x7ff73a9598d3]
+	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
+	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
+	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
+	GetHandleVerifier [0x0x7ff73abacfee+191102]
+	GetHandleVerifier [0x0x7ff73abb50af+224063]
+	GetHandleVerifier [0x0x7ff73ab9af64+117236]
+	GetHandleVerifier [0x0x7ff73ab9b119+117673]
+	GetHandleVerifier [0x0x7ff73ab810a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -666,12 +666,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.99</t>
+          <t>£11.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.99</t>
+          <t>£11.97</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
+	GetHandleVerifier [0x0x7ff73ab91f10+80288]
+	(No symbol) [0x0x7ff73a9102fa]
+	(No symbol) [0x0x7ff73a967cd7]
+	(No symbol) [0x0x7ff73a967f9c]
+	(No symbol) [0x0x7ff73a9bba87]
+	(No symbol) [0x0x7ff73a9903bf]
+	(No symbol) [0x0x7ff73a9b87fb]
+	(No symbol) [0x0x7ff73a990153]
+	(No symbol) [0x0x7ff73a958b02]
+	(No symbol) [0x0x7ff73a9598d3]
+	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
+	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
+	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
+	GetHandleVerifier [0x0x7ff73abacfee+191102]
+	GetHandleVerifier [0x0x7ff73abb50af+224063]
+	GetHandleVerifier [0x0x7ff73ab9af64+117236]
+	GetHandleVerifier [0x0x7ff73ab9b119+117673]
+	GetHandleVerifier [0x0x7ff73ab810a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -788,12 +788,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£15.30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£15.30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
+	GetHandleVerifier [0x0x7ff73ab91f10+80288]
+	(No symbol) [0x0x7ff73a9102fa]
+	(No symbol) [0x0x7ff73a967cd7]
+	(No symbol) [0x0x7ff73a967f9c]
+	(No symbol) [0x0x7ff73a9bba87]
+	(No symbol) [0x0x7ff73a9903bf]
+	(No symbol) [0x0x7ff73a9b87fb]
+	(No symbol) [0x0x7ff73a990153]
+	(No symbol) [0x0x7ff73a958b02]
+	(No symbol) [0x0x7ff73a9598d3]
+	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
+	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
+	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
+	GetHandleVerifier [0x0x7ff73abacfee+191102]
+	GetHandleVerifier [0x0x7ff73abb50af+224063]
+	GetHandleVerifier [0x0x7ff73ab9af64+117236]
+	GetHandleVerifier [0x0x7ff73ab9b119+117673]
+	GetHandleVerifier [0x0x7ff73ab810a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
+	GetHandleVerifier [0x0x7ff73ab91f10+80288]
+	(No symbol) [0x0x7ff73a9102fa]
+	(No symbol) [0x0x7ff73a967cd7]
+	(No symbol) [0x0x7ff73a967f9c]
+	(No symbol) [0x0x7ff73a9bba87]
+	(No symbol) [0x0x7ff73a9903bf]
+	(No symbol) [0x0x7ff73a9b87fb]
+	(No symbol) [0x0x7ff73a990153]
+	(No symbol) [0x0x7ff73a958b02]
+	(No symbol) [0x0x7ff73a9598d3]
+	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
+	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
+	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
+	GetHandleVerifier [0x0x7ff73abacfee+191102]
+	GetHandleVerifier [0x0x7ff73abb50af+224063]
+	GetHandleVerifier [0x0x7ff73ab9af64+117236]
+	GetHandleVerifier [0x0x7ff73ab9b119+117673]
+	GetHandleVerifier [0x0x7ff73ab810a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
+	GetHandleVerifier [0x0x7ff73ab91f10+80288]
+	(No symbol) [0x0x7ff73a9102fa]
+	(No symbol) [0x0x7ff73a967cd7]
+	(No symbol) [0x0x7ff73a967f9c]
+	(No symbol) [0x0x7ff73a9bba87]
+	(No symbol) [0x0x7ff73a9903bf]
+	(No symbol) [0x0x7ff73a9b87fb]
+	(No symbol) [0x0x7ff73a990153]
+	(No symbol) [0x0x7ff73a958b02]
+	(No symbol) [0x0x7ff73a9598d3]
+	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
+	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
+	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
+	GetHandleVerifier [0x0x7ff73abacfee+191102]
+	GetHandleVerifier [0x0x7ff73abb50af+224063]
+	GetHandleVerifier [0x0x7ff73ab9af64+117236]
+	GetHandleVerifier [0x0x7ff73ab9b119+117673]
+	GetHandleVerifier [0x0x7ff73ab810a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£21.75</t>
+          <t>£21.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£21.75</t>
+          <t>£21.70</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
+	GetHandleVerifier [0x0x7ff73ab91f10+80288]
+	(No symbol) [0x0x7ff73a9102fa]
+	(No symbol) [0x0x7ff73a967cd7]
+	(No symbol) [0x0x7ff73a967f9c]
+	(No symbol) [0x0x7ff73a9bba87]
+	(No symbol) [0x0x7ff73a9903bf]
+	(No symbol) [0x0x7ff73a9b87fb]
+	(No symbol) [0x0x7ff73a990153]
+	(No symbol) [0x0x7ff73a958b02]
+	(No symbol) [0x0x7ff73a9598d3]
+	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
+	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
+	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
+	GetHandleVerifier [0x0x7ff73abacfee+191102]
+	GetHandleVerifier [0x0x7ff73abb50af+224063]
+	GetHandleVerifier [0x0x7ff73ab9af64+117236]
+	GetHandleVerifier [0x0x7ff73ab9b119+117673]
+	GetHandleVerifier [0x0x7ff73ab810a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£21.95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£21.95</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
+	GetHandleVerifier [0x0x7ff73ab91f10+80288]
+	(No symbol) [0x0x7ff73a9102fa]
+	(No symbol) [0x0x7ff73a967cd7]
+	(No symbol) [0x0x7ff73a967f9c]
+	(No symbol) [0x0x7ff73a9bba87]
+	(No symbol) [0x0x7ff73a9903bf]
+	(No symbol) [0x0x7ff73a9b87fb]
+	(No symbol) [0x0x7ff73a990153]
+	(No symbol) [0x0x7ff73a958b02]
+	(No symbol) [0x0x7ff73a9598d3]
+	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
+	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
+	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
+	GetHandleVerifier [0x0x7ff73abacfee+191102]
+	GetHandleVerifier [0x0x7ff73abb50af+224063]
+	GetHandleVerifier [0x0x7ff73ab9af64+117236]
+	GetHandleVerifier [0x0x7ff73ab9b119+117673]
+	GetHandleVerifier [0x0x7ff73ab810a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
+	GetHandleVerifier [0x0x7ff73ab91f10+80288]
+	(No symbol) [0x0x7ff73a9102fa]
+	(No symbol) [0x0x7ff73a967cd7]
+	(No symbol) [0x0x7ff73a967f9c]
+	(No symbol) [0x0x7ff73a9bba87]
+	(No symbol) [0x0x7ff73a9903bf]
+	(No symbol) [0x0x7ff73a9b87fb]
+	(No symbol) [0x0x7ff73a990153]
+	(No symbol) [0x0x7ff73a958b02]
+	(No symbol) [0x0x7ff73a9598d3]
+	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
+	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
+	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
+	GetHandleVerifier [0x0x7ff73abacfee+191102]
+	GetHandleVerifier [0x0x7ff73abb50af+224063]
+	GetHandleVerifier [0x0x7ff73ab9af64+117236]
+	GetHandleVerifier [0x0x7ff73ab9b119+117673]
+	GetHandleVerifier [0x0x7ff73ab810a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£27.30</t>
+          <t>£27.27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£27.30</t>
+          <t>£27.27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff72f4c1eb5+80197]
+	GetHandleVerifier [0x0x7ff72f4c1f10+80288]
+	(No symbol) [0x0x7ff72f2402fa]
+	(No symbol) [0x0x7ff72f297cd7]
+	(No symbol) [0x0x7ff72f297f9c]
+	(No symbol) [0x0x7ff72f2eba87]
+	(No symbol) [0x0x7ff72f2c03bf]
+	(No symbol) [0x0x7ff72f2e87fb]
+	(No symbol) [0x0x7ff72f2c0153]
+	(No symbol) [0x0x7ff72f288b02]
+	(No symbol) [0x0x7ff72f2898d3]
+	GetHandleVerifier [0x0x7ff72f77e83d+2949837]
+	GetHandleVerifier [0x0x7ff72f778c6a+2926330]
+	GetHandleVerifier [0x0x7ff72f7986c7+3055959]
+	GetHandleVerifier [0x0x7ff72f4dcfee+191102]
+	GetHandleVerifier [0x0x7ff72f4e50af+224063]
+	GetHandleVerifier [0x0x7ff72f4caf64+117236]
+	GetHandleVerifier [0x0x7ff72f4cb119+117673]
+	GetHandleVerifier [0x0x7ff72f4b10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1637,17 +1637,17 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Regular price
-                  £26.85</t>
+                  £26.82</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.85</t>
+          <t>£26.82</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£26.85</t>
+          <t>£26.82</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff69d501eb5+80197]
+	GetHandleVerifier [0x0x7ff69d501f10+80288]
+	(No symbol) [0x0x7ff69d2802fa]
+	(No symbol) [0x0x7ff69d2d7cd7]
+	(No symbol) [0x0x7ff69d2d7f9c]
+	(No symbol) [0x0x7ff69d32ba87]
+	(No symbol) [0x0x7ff69d3003bf]
+	(No symbol) [0x0x7ff69d3287fb]
+	(No symbol) [0x0x7ff69d300153]
+	(No symbol) [0x0x7ff69d2c8b02]
+	(No symbol) [0x0x7ff69d2c98d3]
+	GetHandleVerifier [0x0x7ff69d7be83d+2949837]
+	GetHandleVerifier [0x0x7ff69d7b8c6a+2926330]
+	GetHandleVerifier [0x0x7ff69d7d86c7+3055959]
+	GetHandleVerifier [0x0x7ff69d51cfee+191102]
+	GetHandleVerifier [0x0x7ff69d5250af+224063]
+	GetHandleVerifier [0x0x7ff69d50af64+117236]
+	GetHandleVerifier [0x0x7ff69d50b119+117673]
+	GetHandleVerifier [0x0x7ff69d4f10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff64f4e1eb5+80197]
+	GetHandleVerifier [0x0x7ff64f4e1f10+80288]
+	(No symbol) [0x0x7ff64f2602fa]
+	(No symbol) [0x0x7ff64f2b7cd7]
+	(No symbol) [0x0x7ff64f2b7f9c]
+	(No symbol) [0x0x7ff64f30ba87]
+	(No symbol) [0x0x7ff64f2e03bf]
+	(No symbol) [0x0x7ff64f3087fb]
+	(No symbol) [0x0x7ff64f2e0153]
+	(No symbol) [0x0x7ff64f2a8b02]
+	(No symbol) [0x0x7ff64f2a98d3]
+	GetHandleVerifier [0x0x7ff64f79e83d+2949837]
+	GetHandleVerifier [0x0x7ff64f798c6a+2926330]
+	GetHandleVerifier [0x0x7ff64f7b86c7+3055959]
+	GetHandleVerifier [0x0x7ff64f4fcfee+191102]
+	GetHandleVerifier [0x0x7ff64f5050af+224063]
+	GetHandleVerifier [0x0x7ff64f4eaf64+117236]
+	GetHandleVerifier [0x0x7ff64f4eb119+117673]
+	GetHandleVerifier [0x0x7ff64f4d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1881,17 +1881,17 @@
       <c r="C13" t="inlineStr">
         <is>
           <t>Regular price
-                  £32.95</t>
+                  £32.92</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£32.95</t>
+          <t>£32.92</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£32.95</t>
+          <t>£32.92</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff64f4e1eb5+80197]
+	GetHandleVerifier [0x0x7ff64f4e1f10+80288]
+	(No symbol) [0x0x7ff64f2602fa]
+	(No symbol) [0x0x7ff64f2b7cd7]
+	(No symbol) [0x0x7ff64f2b7f9c]
+	(No symbol) [0x0x7ff64f30ba87]
+	(No symbol) [0x0x7ff64f2e03bf]
+	(No symbol) [0x0x7ff64f3087fb]
+	(No symbol) [0x0x7ff64f2e0153]
+	(No symbol) [0x0x7ff64f2a8b02]
+	(No symbol) [0x0x7ff64f2a98d3]
+	GetHandleVerifier [0x0x7ff64f79e83d+2949837]
+	GetHandleVerifier [0x0x7ff64f798c6a+2926330]
+	GetHandleVerifier [0x0x7ff64f7b86c7+3055959]
+	GetHandleVerifier [0x0x7ff64f4fcfee+191102]
+	GetHandleVerifier [0x0x7ff64f5050af+224063]
+	GetHandleVerifier [0x0x7ff64f4eaf64+117236]
+	GetHandleVerifier [0x0x7ff64f4eb119+117673]
+	GetHandleVerifier [0x0x7ff64f4d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 522 Server Error: &lt;none&gt; for url: https://imperialhouse-nj.com/contact-us-2/</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2003,17 +2003,17 @@
       <c r="C14" t="inlineStr">
         <is>
           <t>Regular price
-                  £40.20</t>
+                  £40.18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£40.20</t>
+          <t>£40.18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£40.20</t>
+          <t>£40.18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff72cbd1eb5+80197]
+	GetHandleVerifier [0x0x7ff72cbd1f10+80288]
+	(No symbol) [0x0x7ff72c9502fa]
+	(No symbol) [0x0x7ff72c9a7cd7]
+	(No symbol) [0x0x7ff72c9a7f9c]
+	(No symbol) [0x0x7ff72c9fba87]
+	(No symbol) [0x0x7ff72c9d03bf]
+	(No symbol) [0x0x7ff72c9f87fb]
+	(No symbol) [0x0x7ff72c9d0153]
+	(No symbol) [0x0x7ff72c998b02]
+	(No symbol) [0x0x7ff72c9998d3]
+	GetHandleVerifier [0x0x7ff72ce8e83d+2949837]
+	GetHandleVerifier [0x0x7ff72ce88c6a+2926330]
+	GetHandleVerifier [0x0x7ff72cea86c7+3055959]
+	GetHandleVerifier [0x0x7ff72cbecfee+191102]
+	GetHandleVerifier [0x0x7ff72cbf50af+224063]
+	GetHandleVerifier [0x0x7ff72cbdaf64+117236]
+	GetHandleVerifier [0x0x7ff72cbdb119+117673]
+	GetHandleVerifier [0x0x7ff72cbc10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff72cbd1eb5+80197]
+	GetHandleVerifier [0x0x7ff72cbd1f10+80288]
+	(No symbol) [0x0x7ff72c9502fa]
+	(No symbol) [0x0x7ff72c9a7cd7]
+	(No symbol) [0x0x7ff72c9a7f9c]
+	(No symbol) [0x0x7ff72c9fba87]
+	(No symbol) [0x0x7ff72c9d03bf]
+	(No symbol) [0x0x7ff72c9f87fb]
+	(No symbol) [0x0x7ff72c9d0153]
+	(No symbol) [0x0x7ff72c998b02]
+	(No symbol) [0x0x7ff72c9998d3]
+	GetHandleVerifier [0x0x7ff72ce8e83d+2949837]
+	GetHandleVerifier [0x0x7ff72ce88c6a+2926330]
+	GetHandleVerifier [0x0x7ff72cea86c7+3055959]
+	GetHandleVerifier [0x0x7ff72cbecfee+191102]
+	GetHandleVerifier [0x0x7ff72cbf50af+224063]
+	GetHandleVerifier [0x0x7ff72cbdaf64+117236]
+	GetHandleVerifier [0x0x7ff72cbdb119+117673]
+	GetHandleVerifier [0x0x7ff72cbc10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2246,17 +2246,17 @@
       <c r="C16" t="inlineStr">
         <is>
           <t>Regular price
-                  £40.92</t>
+                  £40.89</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£40.92</t>
+          <t>£40.89</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£40.92</t>
+          <t>£40.89</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff72cbd1eb5+80197]
+	GetHandleVerifier [0x0x7ff72cbd1f10+80288]
+	(No symbol) [0x0x7ff72c9502fa]
+	(No symbol) [0x0x7ff72c9a7cd7]
+	(No symbol) [0x0x7ff72c9a7f9c]
+	(No symbol) [0x0x7ff72c9fba87]
+	(No symbol) [0x0x7ff72c9d03bf]
+	(No symbol) [0x0x7ff72c9f87fb]
+	(No symbol) [0x0x7ff72c9d0153]
+	(No symbol) [0x0x7ff72c998b02]
+	(No symbol) [0x0x7ff72c9998d3]
+	GetHandleVerifier [0x0x7ff72ce8e83d+2949837]
+	GetHandleVerifier [0x0x7ff72ce88c6a+2926330]
+	GetHandleVerifier [0x0x7ff72cea86c7+3055959]
+	GetHandleVerifier [0x0x7ff72cbecfee+191102]
+	GetHandleVerifier [0x0x7ff72cbf50af+224063]
+	GetHandleVerifier [0x0x7ff72cbdaf64+117236]
+	GetHandleVerifier [0x0x7ff72cbdb119+117673]
+	GetHandleVerifier [0x0x7ff72cbc10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff72cbd1eb5+80197]
+	GetHandleVerifier [0x0x7ff72cbd1f10+80288]
+	(No symbol) [0x0x7ff72c9502fa]
+	(No symbol) [0x0x7ff72c9a7cd7]
+	(No symbol) [0x0x7ff72c9a7f9c]
+	(No symbol) [0x0x7ff72c9fba87]
+	(No symbol) [0x0x7ff72c9d03bf]
+	(No symbol) [0x0x7ff72c9f87fb]
+	(No symbol) [0x0x7ff72c9d0153]
+	(No symbol) [0x0x7ff72c998b02]
+	(No symbol) [0x0x7ff72c9998d3]
+	GetHandleVerifier [0x0x7ff72ce8e83d+2949837]
+	GetHandleVerifier [0x0x7ff72ce88c6a+2926330]
+	GetHandleVerifier [0x0x7ff72cea86c7+3055959]
+	GetHandleVerifier [0x0x7ff72cbecfee+191102]
+	GetHandleVerifier [0x0x7ff72cbf50af+224063]
+	GetHandleVerifier [0x0x7ff72cbdaf64+117236]
+	GetHandleVerifier [0x0x7ff72cbdb119+117673]
+	GetHandleVerifier [0x0x7ff72cbc10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
+	GetHandleVerifier [0x0x7ff76eca1f10+80288]
+	(No symbol) [0x0x7ff76ea202fa]
+	(No symbol) [0x0x7ff76ea77cd7]
+	(No symbol) [0x0x7ff76ea77f9c]
+	(No symbol) [0x0x7ff76eacba87]
+	(No symbol) [0x0x7ff76eaa03bf]
+	(No symbol) [0x0x7ff76eac87fb]
+	(No symbol) [0x0x7ff76eaa0153]
+	(No symbol) [0x0x7ff76ea68b02]
+	(No symbol) [0x0x7ff76ea698d3]
+	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
+	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
+	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
+	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
+	GetHandleVerifier [0x0x7ff76ecc50af+224063]
+	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
+	GetHandleVerifier [0x0x7ff76ecab119+117673]
+	GetHandleVerifier [0x0x7ff76ec910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
+	GetHandleVerifier [0x0x7ff76eca1f10+80288]
+	(No symbol) [0x0x7ff76ea202fa]
+	(No symbol) [0x0x7ff76ea77cd7]
+	(No symbol) [0x0x7ff76ea77f9c]
+	(No symbol) [0x0x7ff76eacba87]
+	(No symbol) [0x0x7ff76eaa03bf]
+	(No symbol) [0x0x7ff76eac87fb]
+	(No symbol) [0x0x7ff76eaa0153]
+	(No symbol) [0x0x7ff76ea68b02]
+	(No symbol) [0x0x7ff76ea698d3]
+	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
+	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
+	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
+	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
+	GetHandleVerifier [0x0x7ff76ecc50af+224063]
+	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
+	GetHandleVerifier [0x0x7ff76ecab119+117673]
+	GetHandleVerifier [0x0x7ff76ec910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
+	GetHandleVerifier [0x0x7ff76eca1f10+80288]
+	(No symbol) [0x0x7ff76ea202fa]
+	(No symbol) [0x0x7ff76ea77cd7]
+	(No symbol) [0x0x7ff76ea77f9c]
+	(No symbol) [0x0x7ff76eacba87]
+	(No symbol) [0x0x7ff76eaa03bf]
+	(No symbol) [0x0x7ff76eac87fb]
+	(No symbol) [0x0x7ff76eaa0153]
+	(No symbol) [0x0x7ff76ea68b02]
+	(No symbol) [0x0x7ff76ea698d3]
+	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
+	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
+	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
+	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
+	GetHandleVerifier [0x0x7ff76ecc50af+224063]
+	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
+	GetHandleVerifier [0x0x7ff76ecab119+117673]
+	GetHandleVerifier [0x0x7ff76ec910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
+	GetHandleVerifier [0x0x7ff76eca1f10+80288]
+	(No symbol) [0x0x7ff76ea202fa]
+	(No symbol) [0x0x7ff76ea77cd7]
+	(No symbol) [0x0x7ff76ea77f9c]
+	(No symbol) [0x0x7ff76eacba87]
+	(No symbol) [0x0x7ff76eaa03bf]
+	(No symbol) [0x0x7ff76eac87fb]
+	(No symbol) [0x0x7ff76eaa0153]
+	(No symbol) [0x0x7ff76ea68b02]
+	(No symbol) [0x0x7ff76ea698d3]
+	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
+	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
+	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
+	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
+	GetHandleVerifier [0x0x7ff76ecc50af+224063]
+	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
+	GetHandleVerifier [0x0x7ff76ecab119+117673]
+	GetHandleVerifier [0x0x7ff76ec910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
+	GetHandleVerifier [0x0x7ff76eca1f10+80288]
+	(No symbol) [0x0x7ff76ea202fa]
+	(No symbol) [0x0x7ff76ea77cd7]
+	(No symbol) [0x0x7ff76ea77f9c]
+	(No symbol) [0x0x7ff76eacba87]
+	(No symbol) [0x0x7ff76eaa03bf]
+	(No symbol) [0x0x7ff76eac87fb]
+	(No symbol) [0x0x7ff76eaa0153]
+	(No symbol) [0x0x7ff76ea68b02]
+	(No symbol) [0x0x7ff76ea698d3]
+	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
+	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
+	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
+	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
+	GetHandleVerifier [0x0x7ff76ecc50af+224063]
+	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
+	GetHandleVerifier [0x0x7ff76ecab119+117673]
+	GetHandleVerifier [0x0x7ff76ec910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
+	GetHandleVerifier [0x0x7ff76eca1f10+80288]
+	(No symbol) [0x0x7ff76ea202fa]
+	(No symbol) [0x0x7ff76ea77cd7]
+	(No symbol) [0x0x7ff76ea77f9c]
+	(No symbol) [0x0x7ff76eacba87]
+	(No symbol) [0x0x7ff76eaa03bf]
+	(No symbol) [0x0x7ff76eac87fb]
+	(No symbol) [0x0x7ff76eaa0153]
+	(No symbol) [0x0x7ff76ea68b02]
+	(No symbol) [0x0x7ff76ea698d3]
+	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
+	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
+	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
+	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
+	GetHandleVerifier [0x0x7ff76ecc50af+224063]
+	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
+	GetHandleVerifier [0x0x7ff76ecab119+117673]
+	GetHandleVerifier [0x0x7ff76ec910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
+	GetHandleVerifier [0x0x7ff76eca1f10+80288]
+	(No symbol) [0x0x7ff76ea202fa]
+	(No symbol) [0x0x7ff76ea77cd7]
+	(No symbol) [0x0x7ff76ea77f9c]
+	(No symbol) [0x0x7ff76eacba87]
+	(No symbol) [0x0x7ff76eaa03bf]
+	(No symbol) [0x0x7ff76eac87fb]
+	(No symbol) [0x0x7ff76eaa0153]
+	(No symbol) [0x0x7ff76ea68b02]
+	(No symbol) [0x0x7ff76ea698d3]
+	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
+	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
+	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
+	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
+	GetHandleVerifier [0x0x7ff76ecc50af+224063]
+	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
+	GetHandleVerifier [0x0x7ff76ecab119+117673]
+	GetHandleVerifier [0x0x7ff76ec910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
+	GetHandleVerifier [0x0x7ff76eca1f10+80288]
+	(No symbol) [0x0x7ff76ea202fa]
+	(No symbol) [0x0x7ff76ea77cd7]
+	(No symbol) [0x0x7ff76ea77f9c]
+	(No symbol) [0x0x7ff76eacba87]
+	(No symbol) [0x0x7ff76eaa03bf]
+	(No symbol) [0x0x7ff76eac87fb]
+	(No symbol) [0x0x7ff76eaa0153]
+	(No symbol) [0x0x7ff76ea68b02]
+	(No symbol) [0x0x7ff76ea698d3]
+	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
+	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
+	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
+	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
+	GetHandleVerifier [0x0x7ff76ecc50af+224063]
+	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
+	GetHandleVerifier [0x0x7ff76ecab119+117673]
+	GetHandleVerifier [0x0x7ff76ec910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>£1,213.28</t>
+          <t>£1,225.00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-09-2025.xlsx
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
-	GetHandleVerifier [0x0x7ff73ab91f10+80288]
-	(No symbol) [0x0x7ff73a9102fa]
-	(No symbol) [0x0x7ff73a967cd7]
-	(No symbol) [0x0x7ff73a967f9c]
-	(No symbol) [0x0x7ff73a9bba87]
-	(No symbol) [0x0x7ff73a9903bf]
-	(No symbol) [0x0x7ff73a9b87fb]
-	(No symbol) [0x0x7ff73a990153]
-	(No symbol) [0x0x7ff73a958b02]
-	(No symbol) [0x0x7ff73a9598d3]
-	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
-	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
-	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
-	GetHandleVerifier [0x0x7ff73abacfee+191102]
-	GetHandleVerifier [0x0x7ff73abb50af+224063]
-	GetHandleVerifier [0x0x7ff73ab9af64+117236]
-	GetHandleVerifier [0x0x7ff73ab9b119+117673]
-	GetHandleVerifier [0x0x7ff73ab810a8+11064]
+	GetHandleVerifier [0x0x7ff729c01eb5+80197]
+	GetHandleVerifier [0x0x7ff729c01f10+80288]
+	(No symbol) [0x0x7ff7299802fa]
+	(No symbol) [0x0x7ff7299d7cd7]
+	(No symbol) [0x0x7ff7299d7f9c]
+	(No symbol) [0x0x7ff729a2ba87]
+	(No symbol) [0x0x7ff729a003bf]
+	(No symbol) [0x0x7ff729a287fb]
+	(No symbol) [0x0x7ff729a00153]
+	(No symbol) [0x0x7ff7299c8b02]
+	(No symbol) [0x0x7ff7299c98d3]
+	GetHandleVerifier [0x0x7ff729ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff729eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff729ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff729c1cfee+191102]
+	GetHandleVerifier [0x0x7ff729c250af+224063]
+	GetHandleVerifier [0x0x7ff729c0af64+117236]
+	GetHandleVerifier [0x0x7ff729c0b119+117673]
+	GetHandleVerifier [0x0x7ff729bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -661,7 +661,7 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>Regular price
-                  £11.99</t>
+                  £11.97</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
-	GetHandleVerifier [0x0x7ff73ab91f10+80288]
-	(No symbol) [0x0x7ff73a9102fa]
-	(No symbol) [0x0x7ff73a967cd7]
-	(No symbol) [0x0x7ff73a967f9c]
-	(No symbol) [0x0x7ff73a9bba87]
-	(No symbol) [0x0x7ff73a9903bf]
-	(No symbol) [0x0x7ff73a9b87fb]
-	(No symbol) [0x0x7ff73a990153]
-	(No symbol) [0x0x7ff73a958b02]
-	(No symbol) [0x0x7ff73a9598d3]
-	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
-	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
-	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
-	GetHandleVerifier [0x0x7ff73abacfee+191102]
-	GetHandleVerifier [0x0x7ff73abb50af+224063]
-	GetHandleVerifier [0x0x7ff73ab9af64+117236]
-	GetHandleVerifier [0x0x7ff73ab9b119+117673]
-	GetHandleVerifier [0x0x7ff73ab810a8+11064]
+	GetHandleVerifier [0x0x7ff77a531eb5+80197]
+	GetHandleVerifier [0x0x7ff77a531f10+80288]
+	(No symbol) [0x0x7ff77a2b02fa]
+	(No symbol) [0x0x7ff77a307cd7]
+	(No symbol) [0x0x7ff77a307f9c]
+	(No symbol) [0x0x7ff77a35ba87]
+	(No symbol) [0x0x7ff77a3303bf]
+	(No symbol) [0x0x7ff77a3587fb]
+	(No symbol) [0x0x7ff77a330153]
+	(No symbol) [0x0x7ff77a2f8b02]
+	(No symbol) [0x0x7ff77a2f98d3]
+	GetHandleVerifier [0x0x7ff77a7ee83d+2949837]
+	GetHandleVerifier [0x0x7ff77a7e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff77a8086c7+3055959]
+	GetHandleVerifier [0x0x7ff77a54cfee+191102]
+	GetHandleVerifier [0x0x7ff77a5550af+224063]
+	GetHandleVerifier [0x0x7ff77a53af64+117236]
+	GetHandleVerifier [0x0x7ff77a53b119+117673]
+	GetHandleVerifier [0x0x7ff77a5210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -783,7 +783,7 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Regular price
-                  £15.35</t>
+                  £15.30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
-	GetHandleVerifier [0x0x7ff73ab91f10+80288]
-	(No symbol) [0x0x7ff73a9102fa]
-	(No symbol) [0x0x7ff73a967cd7]
-	(No symbol) [0x0x7ff73a967f9c]
-	(No symbol) [0x0x7ff73a9bba87]
-	(No symbol) [0x0x7ff73a9903bf]
-	(No symbol) [0x0x7ff73a9b87fb]
-	(No symbol) [0x0x7ff73a990153]
-	(No symbol) [0x0x7ff73a958b02]
-	(No symbol) [0x0x7ff73a9598d3]
-	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
-	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
-	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
-	GetHandleVerifier [0x0x7ff73abacfee+191102]
-	GetHandleVerifier [0x0x7ff73abb50af+224063]
-	GetHandleVerifier [0x0x7ff73ab9af64+117236]
-	GetHandleVerifier [0x0x7ff73ab9b119+117673]
-	GetHandleVerifier [0x0x7ff73ab810a8+11064]
+	GetHandleVerifier [0x0x7ff639701eb5+80197]
+	GetHandleVerifier [0x0x7ff639701f10+80288]
+	(No symbol) [0x0x7ff6394802fa]
+	(No symbol) [0x0x7ff6394d7cd7]
+	(No symbol) [0x0x7ff6394d7f9c]
+	(No symbol) [0x0x7ff63952ba87]
+	(No symbol) [0x0x7ff6395003bf]
+	(No symbol) [0x0x7ff6395287fb]
+	(No symbol) [0x0x7ff639500153]
+	(No symbol) [0x0x7ff6394c8b02]
+	(No symbol) [0x0x7ff6394c98d3]
+	GetHandleVerifier [0x0x7ff6399be83d+2949837]
+	GetHandleVerifier [0x0x7ff6399b8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6399d86c7+3055959]
+	GetHandleVerifier [0x0x7ff63971cfee+191102]
+	GetHandleVerifier [0x0x7ff6397250af+224063]
+	GetHandleVerifier [0x0x7ff63970af64+117236]
+	GetHandleVerifier [0x0x7ff63970b119+117673]
+	GetHandleVerifier [0x0x7ff6396f10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
-	GetHandleVerifier [0x0x7ff73ab91f10+80288]
-	(No symbol) [0x0x7ff73a9102fa]
-	(No symbol) [0x0x7ff73a967cd7]
-	(No symbol) [0x0x7ff73a967f9c]
-	(No symbol) [0x0x7ff73a9bba87]
-	(No symbol) [0x0x7ff73a9903bf]
-	(No symbol) [0x0x7ff73a9b87fb]
-	(No symbol) [0x0x7ff73a990153]
-	(No symbol) [0x0x7ff73a958b02]
-	(No symbol) [0x0x7ff73a9598d3]
-	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
-	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
-	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
-	GetHandleVerifier [0x0x7ff73abacfee+191102]
-	GetHandleVerifier [0x0x7ff73abb50af+224063]
-	GetHandleVerifier [0x0x7ff73ab9af64+117236]
-	GetHandleVerifier [0x0x7ff73ab9b119+117673]
-	GetHandleVerifier [0x0x7ff73ab810a8+11064]
+	GetHandleVerifier [0x0x7ff7de8b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7de8b1f10+80288]
+	(No symbol) [0x0x7ff7de6302fa]
+	(No symbol) [0x0x7ff7de687cd7]
+	(No symbol) [0x0x7ff7de687f9c]
+	(No symbol) [0x0x7ff7de6dba87]
+	(No symbol) [0x0x7ff7de6b03bf]
+	(No symbol) [0x0x7ff7de6d87fb]
+	(No symbol) [0x0x7ff7de6b0153]
+	(No symbol) [0x0x7ff7de678b02]
+	(No symbol) [0x0x7ff7de6798d3]
+	GetHandleVerifier [0x0x7ff7deb6e83d+2949837]
+	GetHandleVerifier [0x0x7ff7deb68c6a+2926330]
+	GetHandleVerifier [0x0x7ff7deb886c7+3055959]
+	GetHandleVerifier [0x0x7ff7de8ccfee+191102]
+	GetHandleVerifier [0x0x7ff7de8d50af+224063]
+	GetHandleVerifier [0x0x7ff7de8baf64+117236]
+	GetHandleVerifier [0x0x7ff7de8bb119+117673]
+	GetHandleVerifier [0x0x7ff7de8a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
-	GetHandleVerifier [0x0x7ff73ab91f10+80288]
-	(No symbol) [0x0x7ff73a9102fa]
-	(No symbol) [0x0x7ff73a967cd7]
-	(No symbol) [0x0x7ff73a967f9c]
-	(No symbol) [0x0x7ff73a9bba87]
-	(No symbol) [0x0x7ff73a9903bf]
-	(No symbol) [0x0x7ff73a9b87fb]
-	(No symbol) [0x0x7ff73a990153]
-	(No symbol) [0x0x7ff73a958b02]
-	(No symbol) [0x0x7ff73a9598d3]
-	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
-	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
-	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
-	GetHandleVerifier [0x0x7ff73abacfee+191102]
-	GetHandleVerifier [0x0x7ff73abb50af+224063]
-	GetHandleVerifier [0x0x7ff73ab9af64+117236]
-	GetHandleVerifier [0x0x7ff73ab9b119+117673]
-	GetHandleVerifier [0x0x7ff73ab810a8+11064]
+	GetHandleVerifier [0x0x7ff628bc1eb5+80197]
+	GetHandleVerifier [0x0x7ff628bc1f10+80288]
+	(No symbol) [0x0x7ff6289402fa]
+	(No symbol) [0x0x7ff628997cd7]
+	(No symbol) [0x0x7ff628997f9c]
+	(No symbol) [0x0x7ff6289eba87]
+	(No symbol) [0x0x7ff6289c03bf]
+	(No symbol) [0x0x7ff6289e87fb]
+	(No symbol) [0x0x7ff6289c0153]
+	(No symbol) [0x0x7ff628988b02]
+	(No symbol) [0x0x7ff6289898d3]
+	GetHandleVerifier [0x0x7ff628e7e83d+2949837]
+	GetHandleVerifier [0x0x7ff628e78c6a+2926330]
+	GetHandleVerifier [0x0x7ff628e986c7+3055959]
+	GetHandleVerifier [0x0x7ff628bdcfee+191102]
+	GetHandleVerifier [0x0x7ff628be50af+224063]
+	GetHandleVerifier [0x0x7ff628bcaf64+117236]
+	GetHandleVerifier [0x0x7ff628bcb119+117673]
+	GetHandleVerifier [0x0x7ff628bb10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1149,7 +1149,7 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>Regular price
-                  £21.75</t>
+                  £21.70</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
-	GetHandleVerifier [0x0x7ff73ab91f10+80288]
-	(No symbol) [0x0x7ff73a9102fa]
-	(No symbol) [0x0x7ff73a967cd7]
-	(No symbol) [0x0x7ff73a967f9c]
-	(No symbol) [0x0x7ff73a9bba87]
-	(No symbol) [0x0x7ff73a9903bf]
-	(No symbol) [0x0x7ff73a9b87fb]
-	(No symbol) [0x0x7ff73a990153]
-	(No symbol) [0x0x7ff73a958b02]
-	(No symbol) [0x0x7ff73a9598d3]
-	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
-	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
-	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
-	GetHandleVerifier [0x0x7ff73abacfee+191102]
-	GetHandleVerifier [0x0x7ff73abb50af+224063]
-	GetHandleVerifier [0x0x7ff73ab9af64+117236]
-	GetHandleVerifier [0x0x7ff73ab9b119+117673]
-	GetHandleVerifier [0x0x7ff73ab810a8+11064]
+	GetHandleVerifier [0x0x7ff792391eb5+80197]
+	GetHandleVerifier [0x0x7ff792391f10+80288]
+	(No symbol) [0x0x7ff7921102fa]
+	(No symbol) [0x0x7ff792167cd7]
+	(No symbol) [0x0x7ff792167f9c]
+	(No symbol) [0x0x7ff7921bba87]
+	(No symbol) [0x0x7ff7921903bf]
+	(No symbol) [0x0x7ff7921b87fb]
+	(No symbol) [0x0x7ff792190153]
+	(No symbol) [0x0x7ff792158b02]
+	(No symbol) [0x0x7ff7921598d3]
+	GetHandleVerifier [0x0x7ff79264e83d+2949837]
+	GetHandleVerifier [0x0x7ff792648c6a+2926330]
+	GetHandleVerifier [0x0x7ff7926686c7+3055959]
+	GetHandleVerifier [0x0x7ff7923acfee+191102]
+	GetHandleVerifier [0x0x7ff7923b50af+224063]
+	GetHandleVerifier [0x0x7ff79239af64+117236]
+	GetHandleVerifier [0x0x7ff79239b119+117673]
+	GetHandleVerifier [0x0x7ff7923810a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1271,7 +1271,7 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Regular price
-                  £22.00</t>
+                  £21.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
-	GetHandleVerifier [0x0x7ff73ab91f10+80288]
-	(No symbol) [0x0x7ff73a9102fa]
-	(No symbol) [0x0x7ff73a967cd7]
-	(No symbol) [0x0x7ff73a967f9c]
-	(No symbol) [0x0x7ff73a9bba87]
-	(No symbol) [0x0x7ff73a9903bf]
-	(No symbol) [0x0x7ff73a9b87fb]
-	(No symbol) [0x0x7ff73a990153]
-	(No symbol) [0x0x7ff73a958b02]
-	(No symbol) [0x0x7ff73a9598d3]
-	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
-	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
-	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
-	GetHandleVerifier [0x0x7ff73abacfee+191102]
-	GetHandleVerifier [0x0x7ff73abb50af+224063]
-	GetHandleVerifier [0x0x7ff73ab9af64+117236]
-	GetHandleVerifier [0x0x7ff73ab9b119+117673]
-	GetHandleVerifier [0x0x7ff73ab810a8+11064]
+	GetHandleVerifier [0x0x7ff6b6c91eb5+80197]
+	GetHandleVerifier [0x0x7ff6b6c91f10+80288]
+	(No symbol) [0x0x7ff6b6a102fa]
+	(No symbol) [0x0x7ff6b6a67cd7]
+	(No symbol) [0x0x7ff6b6a67f9c]
+	(No symbol) [0x0x7ff6b6abba87]
+	(No symbol) [0x0x7ff6b6a903bf]
+	(No symbol) [0x0x7ff6b6ab87fb]
+	(No symbol) [0x0x7ff6b6a90153]
+	(No symbol) [0x0x7ff6b6a58b02]
+	(No symbol) [0x0x7ff6b6a598d3]
+	GetHandleVerifier [0x0x7ff6b6f4e83d+2949837]
+	GetHandleVerifier [0x0x7ff6b6f48c6a+2926330]
+	GetHandleVerifier [0x0x7ff6b6f686c7+3055959]
+	GetHandleVerifier [0x0x7ff6b6cacfee+191102]
+	GetHandleVerifier [0x0x7ff6b6cb50af+224063]
+	GetHandleVerifier [0x0x7ff6b6c9af64+117236]
+	GetHandleVerifier [0x0x7ff6b6c9b119+117673]
+	GetHandleVerifier [0x0x7ff6b6c810a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1393,7 +1393,7 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Regular price
-                  £25.20</t>
+                  £25.18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff73ab91eb5+80197]
-	GetHandleVerifier [0x0x7ff73ab91f10+80288]
-	(No symbol) [0x0x7ff73a9102fa]
-	(No symbol) [0x0x7ff73a967cd7]
-	(No symbol) [0x0x7ff73a967f9c]
-	(No symbol) [0x0x7ff73a9bba87]
-	(No symbol) [0x0x7ff73a9903bf]
-	(No symbol) [0x0x7ff73a9b87fb]
-	(No symbol) [0x0x7ff73a990153]
-	(No symbol) [0x0x7ff73a958b02]
-	(No symbol) [0x0x7ff73a9598d3]
-	GetHandleVerifier [0x0x7ff73ae4e83d+2949837]
-	GetHandleVerifier [0x0x7ff73ae48c6a+2926330]
-	GetHandleVerifier [0x0x7ff73ae686c7+3055959]
-	GetHandleVerifier [0x0x7ff73abacfee+191102]
-	GetHandleVerifier [0x0x7ff73abb50af+224063]
-	GetHandleVerifier [0x0x7ff73ab9af64+117236]
-	GetHandleVerifier [0x0x7ff73ab9b119+117673]
-	GetHandleVerifier [0x0x7ff73ab810a8+11064]
+	GetHandleVerifier [0x0x7ff623691eb5+80197]
+	GetHandleVerifier [0x0x7ff623691f10+80288]
+	(No symbol) [0x0x7ff6234102fa]
+	(No symbol) [0x0x7ff623467cd7]
+	(No symbol) [0x0x7ff623467f9c]
+	(No symbol) [0x0x7ff6234bba87]
+	(No symbol) [0x0x7ff6234903bf]
+	(No symbol) [0x0x7ff6234b87fb]
+	(No symbol) [0x0x7ff623490153]
+	(No symbol) [0x0x7ff623458b02]
+	(No symbol) [0x0x7ff6234598d3]
+	GetHandleVerifier [0x0x7ff62394e83d+2949837]
+	GetHandleVerifier [0x0x7ff623948c6a+2926330]
+	GetHandleVerifier [0x0x7ff6239686c7+3055959]
+	GetHandleVerifier [0x0x7ff6236acfee+191102]
+	GetHandleVerifier [0x0x7ff6236b50af+224063]
+	GetHandleVerifier [0x0x7ff62369af64+117236]
+	GetHandleVerifier [0x0x7ff62369b119+117673]
+	GetHandleVerifier [0x0x7ff6236810a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1515,7 +1515,7 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>Regular price
-                  £27.30</t>
+                  £27.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72f4c1eb5+80197]
-	GetHandleVerifier [0x0x7ff72f4c1f10+80288]
-	(No symbol) [0x0x7ff72f2402fa]
-	(No symbol) [0x0x7ff72f297cd7]
-	(No symbol) [0x0x7ff72f297f9c]
-	(No symbol) [0x0x7ff72f2eba87]
-	(No symbol) [0x0x7ff72f2c03bf]
-	(No symbol) [0x0x7ff72f2e87fb]
-	(No symbol) [0x0x7ff72f2c0153]
-	(No symbol) [0x0x7ff72f288b02]
-	(No symbol) [0x0x7ff72f2898d3]
-	GetHandleVerifier [0x0x7ff72f77e83d+2949837]
-	GetHandleVerifier [0x0x7ff72f778c6a+2926330]
-	GetHandleVerifier [0x0x7ff72f7986c7+3055959]
-	GetHandleVerifier [0x0x7ff72f4dcfee+191102]
-	GetHandleVerifier [0x0x7ff72f4e50af+224063]
-	GetHandleVerifier [0x0x7ff72f4caf64+117236]
-	GetHandleVerifier [0x0x7ff72f4cb119+117673]
-	GetHandleVerifier [0x0x7ff72f4b10a8+11064]
+	GetHandleVerifier [0x0x7ff65ebb1eb5+80197]
+	GetHandleVerifier [0x0x7ff65ebb1f10+80288]
+	(No symbol) [0x0x7ff65e9302fa]
+	(No symbol) [0x0x7ff65e987cd7]
+	(No symbol) [0x0x7ff65e987f9c]
+	(No symbol) [0x0x7ff65e9dba87]
+	(No symbol) [0x0x7ff65e9b03bf]
+	(No symbol) [0x0x7ff65e9d87fb]
+	(No symbol) [0x0x7ff65e9b0153]
+	(No symbol) [0x0x7ff65e978b02]
+	(No symbol) [0x0x7ff65e9798d3]
+	GetHandleVerifier [0x0x7ff65ee6e83d+2949837]
+	GetHandleVerifier [0x0x7ff65ee68c6a+2926330]
+	GetHandleVerifier [0x0x7ff65ee886c7+3055959]
+	GetHandleVerifier [0x0x7ff65ebccfee+191102]
+	GetHandleVerifier [0x0x7ff65ebd50af+224063]
+	GetHandleVerifier [0x0x7ff65ebbaf64+117236]
+	GetHandleVerifier [0x0x7ff65ebbb119+117673]
+	GetHandleVerifier [0x0x7ff65eba10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69d501eb5+80197]
-	GetHandleVerifier [0x0x7ff69d501f10+80288]
-	(No symbol) [0x0x7ff69d2802fa]
-	(No symbol) [0x0x7ff69d2d7cd7]
-	(No symbol) [0x0x7ff69d2d7f9c]
-	(No symbol) [0x0x7ff69d32ba87]
-	(No symbol) [0x0x7ff69d3003bf]
-	(No symbol) [0x0x7ff69d3287fb]
-	(No symbol) [0x0x7ff69d300153]
-	(No symbol) [0x0x7ff69d2c8b02]
-	(No symbol) [0x0x7ff69d2c98d3]
-	GetHandleVerifier [0x0x7ff69d7be83d+2949837]
-	GetHandleVerifier [0x0x7ff69d7b8c6a+2926330]
-	GetHandleVerifier [0x0x7ff69d7d86c7+3055959]
-	GetHandleVerifier [0x0x7ff69d51cfee+191102]
-	GetHandleVerifier [0x0x7ff69d5250af+224063]
-	GetHandleVerifier [0x0x7ff69d50af64+117236]
-	GetHandleVerifier [0x0x7ff69d50b119+117673]
-	GetHandleVerifier [0x0x7ff69d4f10a8+11064]
+	GetHandleVerifier [0x0x7ff65ebb1eb5+80197]
+	GetHandleVerifier [0x0x7ff65ebb1f10+80288]
+	(No symbol) [0x0x7ff65e9302fa]
+	(No symbol) [0x0x7ff65e987cd7]
+	(No symbol) [0x0x7ff65e987f9c]
+	(No symbol) [0x0x7ff65e9dba87]
+	(No symbol) [0x0x7ff65e9b03bf]
+	(No symbol) [0x0x7ff65e9d87fb]
+	(No symbol) [0x0x7ff65e9b0153]
+	(No symbol) [0x0x7ff65e978b02]
+	(No symbol) [0x0x7ff65e9798d3]
+	GetHandleVerifier [0x0x7ff65ee6e83d+2949837]
+	GetHandleVerifier [0x0x7ff65ee68c6a+2926330]
+	GetHandleVerifier [0x0x7ff65ee886c7+3055959]
+	GetHandleVerifier [0x0x7ff65ebccfee+191102]
+	GetHandleVerifier [0x0x7ff65ebd50af+224063]
+	GetHandleVerifier [0x0x7ff65ebbaf64+117236]
+	GetHandleVerifier [0x0x7ff65ebbb119+117673]
+	GetHandleVerifier [0x0x7ff65eba10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64f4e1eb5+80197]
-	GetHandleVerifier [0x0x7ff64f4e1f10+80288]
-	(No symbol) [0x0x7ff64f2602fa]
-	(No symbol) [0x0x7ff64f2b7cd7]
-	(No symbol) [0x0x7ff64f2b7f9c]
-	(No symbol) [0x0x7ff64f30ba87]
-	(No symbol) [0x0x7ff64f2e03bf]
-	(No symbol) [0x0x7ff64f3087fb]
-	(No symbol) [0x0x7ff64f2e0153]
-	(No symbol) [0x0x7ff64f2a8b02]
-	(No symbol) [0x0x7ff64f2a98d3]
-	GetHandleVerifier [0x0x7ff64f79e83d+2949837]
-	GetHandleVerifier [0x0x7ff64f798c6a+2926330]
-	GetHandleVerifier [0x0x7ff64f7b86c7+3055959]
-	GetHandleVerifier [0x0x7ff64f4fcfee+191102]
-	GetHandleVerifier [0x0x7ff64f5050af+224063]
-	GetHandleVerifier [0x0x7ff64f4eaf64+117236]
-	GetHandleVerifier [0x0x7ff64f4eb119+117673]
-	GetHandleVerifier [0x0x7ff64f4d10a8+11064]
+	GetHandleVerifier [0x0x7ff65ebb1eb5+80197]
+	GetHandleVerifier [0x0x7ff65ebb1f10+80288]
+	(No symbol) [0x0x7ff65e9302fa]
+	(No symbol) [0x0x7ff65e987cd7]
+	(No symbol) [0x0x7ff65e987f9c]
+	(No symbol) [0x0x7ff65e9dba87]
+	(No symbol) [0x0x7ff65e9b03bf]
+	(No symbol) [0x0x7ff65e9d87fb]
+	(No symbol) [0x0x7ff65e9b0153]
+	(No symbol) [0x0x7ff65e978b02]
+	(No symbol) [0x0x7ff65e9798d3]
+	GetHandleVerifier [0x0x7ff65ee6e83d+2949837]
+	GetHandleVerifier [0x0x7ff65ee68c6a+2926330]
+	GetHandleVerifier [0x0x7ff65ee886c7+3055959]
+	GetHandleVerifier [0x0x7ff65ebccfee+191102]
+	GetHandleVerifier [0x0x7ff65ebd50af+224063]
+	GetHandleVerifier [0x0x7ff65ebbaf64+117236]
+	GetHandleVerifier [0x0x7ff65ebbb119+117673]
+	GetHandleVerifier [0x0x7ff65eba10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64f4e1eb5+80197]
-	GetHandleVerifier [0x0x7ff64f4e1f10+80288]
-	(No symbol) [0x0x7ff64f2602fa]
-	(No symbol) [0x0x7ff64f2b7cd7]
-	(No symbol) [0x0x7ff64f2b7f9c]
-	(No symbol) [0x0x7ff64f30ba87]
-	(No symbol) [0x0x7ff64f2e03bf]
-	(No symbol) [0x0x7ff64f3087fb]
-	(No symbol) [0x0x7ff64f2e0153]
-	(No symbol) [0x0x7ff64f2a8b02]
-	(No symbol) [0x0x7ff64f2a98d3]
-	GetHandleVerifier [0x0x7ff64f79e83d+2949837]
-	GetHandleVerifier [0x0x7ff64f798c6a+2926330]
-	GetHandleVerifier [0x0x7ff64f7b86c7+3055959]
-	GetHandleVerifier [0x0x7ff64f4fcfee+191102]
-	GetHandleVerifier [0x0x7ff64f5050af+224063]
-	GetHandleVerifier [0x0x7ff64f4eaf64+117236]
-	GetHandleVerifier [0x0x7ff64f4eb119+117673]
-	GetHandleVerifier [0x0x7ff64f4d10a8+11064]
+	GetHandleVerifier [0x0x7ff65ebb1eb5+80197]
+	GetHandleVerifier [0x0x7ff65ebb1f10+80288]
+	(No symbol) [0x0x7ff65e9302fa]
+	(No symbol) [0x0x7ff65e987cd7]
+	(No symbol) [0x0x7ff65e987f9c]
+	(No symbol) [0x0x7ff65e9dba87]
+	(No symbol) [0x0x7ff65e9b03bf]
+	(No symbol) [0x0x7ff65e9d87fb]
+	(No symbol) [0x0x7ff65e9b0153]
+	(No symbol) [0x0x7ff65e978b02]
+	(No symbol) [0x0x7ff65e9798d3]
+	GetHandleVerifier [0x0x7ff65ee6e83d+2949837]
+	GetHandleVerifier [0x0x7ff65ee68c6a+2926330]
+	GetHandleVerifier [0x0x7ff65ee886c7+3055959]
+	GetHandleVerifier [0x0x7ff65ebccfee+191102]
+	GetHandleVerifier [0x0x7ff65ebd50af+224063]
+	GetHandleVerifier [0x0x7ff65ebbaf64+117236]
+	GetHandleVerifier [0x0x7ff65ebbb119+117673]
+	GetHandleVerifier [0x0x7ff65eba10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 522 Server Error: &lt;none&gt; for url: https://imperialhouse-nj.com/contact-us-2/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£40.20</t>
+          <t>£40.18</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72cbd1eb5+80197]
-	GetHandleVerifier [0x0x7ff72cbd1f10+80288]
-	(No symbol) [0x0x7ff72c9502fa]
-	(No symbol) [0x0x7ff72c9a7cd7]
-	(No symbol) [0x0x7ff72c9a7f9c]
-	(No symbol) [0x0x7ff72c9fba87]
-	(No symbol) [0x0x7ff72c9d03bf]
-	(No symbol) [0x0x7ff72c9f87fb]
-	(No symbol) [0x0x7ff72c9d0153]
-	(No symbol) [0x0x7ff72c998b02]
-	(No symbol) [0x0x7ff72c9998d3]
-	GetHandleVerifier [0x0x7ff72ce8e83d+2949837]
-	GetHandleVerifier [0x0x7ff72ce88c6a+2926330]
-	GetHandleVerifier [0x0x7ff72cea86c7+3055959]
-	GetHandleVerifier [0x0x7ff72cbecfee+191102]
-	GetHandleVerifier [0x0x7ff72cbf50af+224063]
-	GetHandleVerifier [0x0x7ff72cbdaf64+117236]
-	GetHandleVerifier [0x0x7ff72cbdb119+117673]
-	GetHandleVerifier [0x0x7ff72cbc10a8+11064]
+	GetHandleVerifier [0x0x7ff65e681eb5+80197]
+	GetHandleVerifier [0x0x7ff65e681f10+80288]
+	(No symbol) [0x0x7ff65e4002fa]
+	(No symbol) [0x0x7ff65e457cd7]
+	(No symbol) [0x0x7ff65e457f9c]
+	(No symbol) [0x0x7ff65e4aba87]
+	(No symbol) [0x0x7ff65e4803bf]
+	(No symbol) [0x0x7ff65e4a87fb]
+	(No symbol) [0x0x7ff65e480153]
+	(No symbol) [0x0x7ff65e448b02]
+	(No symbol) [0x0x7ff65e4498d3]
+	GetHandleVerifier [0x0x7ff65e93e83d+2949837]
+	GetHandleVerifier [0x0x7ff65e938c6a+2926330]
+	GetHandleVerifier [0x0x7ff65e9586c7+3055959]
+	GetHandleVerifier [0x0x7ff65e69cfee+191102]
+	GetHandleVerifier [0x0x7ff65e6a50af+224063]
+	GetHandleVerifier [0x0x7ff65e68af64+117236]
+	GetHandleVerifier [0x0x7ff65e68b119+117673]
+	GetHandleVerifier [0x0x7ff65e6710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72cbd1eb5+80197]
-	GetHandleVerifier [0x0x7ff72cbd1f10+80288]
-	(No symbol) [0x0x7ff72c9502fa]
-	(No symbol) [0x0x7ff72c9a7cd7]
-	(No symbol) [0x0x7ff72c9a7f9c]
-	(No symbol) [0x0x7ff72c9fba87]
-	(No symbol) [0x0x7ff72c9d03bf]
-	(No symbol) [0x0x7ff72c9f87fb]
-	(No symbol) [0x0x7ff72c9d0153]
-	(No symbol) [0x0x7ff72c998b02]
-	(No symbol) [0x0x7ff72c9998d3]
-	GetHandleVerifier [0x0x7ff72ce8e83d+2949837]
-	GetHandleVerifier [0x0x7ff72ce88c6a+2926330]
-	GetHandleVerifier [0x0x7ff72cea86c7+3055959]
-	GetHandleVerifier [0x0x7ff72cbecfee+191102]
-	GetHandleVerifier [0x0x7ff72cbf50af+224063]
-	GetHandleVerifier [0x0x7ff72cbdaf64+117236]
-	GetHandleVerifier [0x0x7ff72cbdb119+117673]
-	GetHandleVerifier [0x0x7ff72cbc10a8+11064]
+	GetHandleVerifier [0x0x7ff65e681eb5+80197]
+	GetHandleVerifier [0x0x7ff65e681f10+80288]
+	(No symbol) [0x0x7ff65e4002fa]
+	(No symbol) [0x0x7ff65e457cd7]
+	(No symbol) [0x0x7ff65e457f9c]
+	(No symbol) [0x0x7ff65e4aba87]
+	(No symbol) [0x0x7ff65e4803bf]
+	(No symbol) [0x0x7ff65e4a87fb]
+	(No symbol) [0x0x7ff65e480153]
+	(No symbol) [0x0x7ff65e448b02]
+	(No symbol) [0x0x7ff65e4498d3]
+	GetHandleVerifier [0x0x7ff65e93e83d+2949837]
+	GetHandleVerifier [0x0x7ff65e938c6a+2926330]
+	GetHandleVerifier [0x0x7ff65e9586c7+3055959]
+	GetHandleVerifier [0x0x7ff65e69cfee+191102]
+	GetHandleVerifier [0x0x7ff65e6a50af+224063]
+	GetHandleVerifier [0x0x7ff65e68af64+117236]
+	GetHandleVerifier [0x0x7ff65e68b119+117673]
+	GetHandleVerifier [0x0x7ff65e6710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72cbd1eb5+80197]
-	GetHandleVerifier [0x0x7ff72cbd1f10+80288]
-	(No symbol) [0x0x7ff72c9502fa]
-	(No symbol) [0x0x7ff72c9a7cd7]
-	(No symbol) [0x0x7ff72c9a7f9c]
-	(No symbol) [0x0x7ff72c9fba87]
-	(No symbol) [0x0x7ff72c9d03bf]
-	(No symbol) [0x0x7ff72c9f87fb]
-	(No symbol) [0x0x7ff72c9d0153]
-	(No symbol) [0x0x7ff72c998b02]
-	(No symbol) [0x0x7ff72c9998d3]
-	GetHandleVerifier [0x0x7ff72ce8e83d+2949837]
-	GetHandleVerifier [0x0x7ff72ce88c6a+2926330]
-	GetHandleVerifier [0x0x7ff72cea86c7+3055959]
-	GetHandleVerifier [0x0x7ff72cbecfee+191102]
-	GetHandleVerifier [0x0x7ff72cbf50af+224063]
-	GetHandleVerifier [0x0x7ff72cbdaf64+117236]
-	GetHandleVerifier [0x0x7ff72cbdb119+117673]
-	GetHandleVerifier [0x0x7ff72cbc10a8+11064]
+	GetHandleVerifier [0x0x7ff65e681eb5+80197]
+	GetHandleVerifier [0x0x7ff65e681f10+80288]
+	(No symbol) [0x0x7ff65e4002fa]
+	(No symbol) [0x0x7ff65e457cd7]
+	(No symbol) [0x0x7ff65e457f9c]
+	(No symbol) [0x0x7ff65e4aba87]
+	(No symbol) [0x0x7ff65e4803bf]
+	(No symbol) [0x0x7ff65e4a87fb]
+	(No symbol) [0x0x7ff65e480153]
+	(No symbol) [0x0x7ff65e448b02]
+	(No symbol) [0x0x7ff65e4498d3]
+	GetHandleVerifier [0x0x7ff65e93e83d+2949837]
+	GetHandleVerifier [0x0x7ff65e938c6a+2926330]
+	GetHandleVerifier [0x0x7ff65e9586c7+3055959]
+	GetHandleVerifier [0x0x7ff65e69cfee+191102]
+	GetHandleVerifier [0x0x7ff65e6a50af+224063]
+	GetHandleVerifier [0x0x7ff65e68af64+117236]
+	GetHandleVerifier [0x0x7ff65e68b119+117673]
+	GetHandleVerifier [0x0x7ff65e6710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72cbd1eb5+80197]
-	GetHandleVerifier [0x0x7ff72cbd1f10+80288]
-	(No symbol) [0x0x7ff72c9502fa]
-	(No symbol) [0x0x7ff72c9a7cd7]
-	(No symbol) [0x0x7ff72c9a7f9c]
-	(No symbol) [0x0x7ff72c9fba87]
-	(No symbol) [0x0x7ff72c9d03bf]
-	(No symbol) [0x0x7ff72c9f87fb]
-	(No symbol) [0x0x7ff72c9d0153]
-	(No symbol) [0x0x7ff72c998b02]
-	(No symbol) [0x0x7ff72c9998d3]
-	GetHandleVerifier [0x0x7ff72ce8e83d+2949837]
-	GetHandleVerifier [0x0x7ff72ce88c6a+2926330]
-	GetHandleVerifier [0x0x7ff72cea86c7+3055959]
-	GetHandleVerifier [0x0x7ff72cbecfee+191102]
-	GetHandleVerifier [0x0x7ff72cbf50af+224063]
-	GetHandleVerifier [0x0x7ff72cbdaf64+117236]
-	GetHandleVerifier [0x0x7ff72cbdb119+117673]
-	GetHandleVerifier [0x0x7ff72cbc10a8+11064]
+	GetHandleVerifier [0x0x7ff65e681eb5+80197]
+	GetHandleVerifier [0x0x7ff65e681f10+80288]
+	(No symbol) [0x0x7ff65e4002fa]
+	(No symbol) [0x0x7ff65e457cd7]
+	(No symbol) [0x0x7ff65e457f9c]
+	(No symbol) [0x0x7ff65e4aba87]
+	(No symbol) [0x0x7ff65e4803bf]
+	(No symbol) [0x0x7ff65e4a87fb]
+	(No symbol) [0x0x7ff65e480153]
+	(No symbol) [0x0x7ff65e448b02]
+	(No symbol) [0x0x7ff65e4498d3]
+	GetHandleVerifier [0x0x7ff65e93e83d+2949837]
+	GetHandleVerifier [0x0x7ff65e938c6a+2926330]
+	GetHandleVerifier [0x0x7ff65e9586c7+3055959]
+	GetHandleVerifier [0x0x7ff65e69cfee+191102]
+	GetHandleVerifier [0x0x7ff65e6a50af+224063]
+	GetHandleVerifier [0x0x7ff65e68af64+117236]
+	GetHandleVerifier [0x0x7ff65e68b119+117673]
+	GetHandleVerifier [0x0x7ff65e6710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
-	GetHandleVerifier [0x0x7ff76eca1f10+80288]
-	(No symbol) [0x0x7ff76ea202fa]
-	(No symbol) [0x0x7ff76ea77cd7]
-	(No symbol) [0x0x7ff76ea77f9c]
-	(No symbol) [0x0x7ff76eacba87]
-	(No symbol) [0x0x7ff76eaa03bf]
-	(No symbol) [0x0x7ff76eac87fb]
-	(No symbol) [0x0x7ff76eaa0153]
-	(No symbol) [0x0x7ff76ea68b02]
-	(No symbol) [0x0x7ff76ea698d3]
-	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
-	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
-	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
-	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
-	GetHandleVerifier [0x0x7ff76ecc50af+224063]
-	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
-	GetHandleVerifier [0x0x7ff76ecab119+117673]
-	GetHandleVerifier [0x0x7ff76ec910a8+11064]
+	GetHandleVerifier [0x0x7ff65e681eb5+80197]
+	GetHandleVerifier [0x0x7ff65e681f10+80288]
+	(No symbol) [0x0x7ff65e4002fa]
+	(No symbol) [0x0x7ff65e457cd7]
+	(No symbol) [0x0x7ff65e457f9c]
+	(No symbol) [0x0x7ff65e4aba87]
+	(No symbol) [0x0x7ff65e4803bf]
+	(No symbol) [0x0x7ff65e4a87fb]
+	(No symbol) [0x0x7ff65e480153]
+	(No symbol) [0x0x7ff65e448b02]
+	(No symbol) [0x0x7ff65e4498d3]
+	GetHandleVerifier [0x0x7ff65e93e83d+2949837]
+	GetHandleVerifier [0x0x7ff65e938c6a+2926330]
+	GetHandleVerifier [0x0x7ff65e9586c7+3055959]
+	GetHandleVerifier [0x0x7ff65e69cfee+191102]
+	GetHandleVerifier [0x0x7ff65e6a50af+224063]
+	GetHandleVerifier [0x0x7ff65e68af64+117236]
+	GetHandleVerifier [0x0x7ff65e68b119+117673]
+	GetHandleVerifier [0x0x7ff65e6710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
-	GetHandleVerifier [0x0x7ff76eca1f10+80288]
-	(No symbol) [0x0x7ff76ea202fa]
-	(No symbol) [0x0x7ff76ea77cd7]
-	(No symbol) [0x0x7ff76ea77f9c]
-	(No symbol) [0x0x7ff76eacba87]
-	(No symbol) [0x0x7ff76eaa03bf]
-	(No symbol) [0x0x7ff76eac87fb]
-	(No symbol) [0x0x7ff76eaa0153]
-	(No symbol) [0x0x7ff76ea68b02]
-	(No symbol) [0x0x7ff76ea698d3]
-	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
-	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
-	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
-	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
-	GetHandleVerifier [0x0x7ff76ecc50af+224063]
-	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
-	GetHandleVerifier [0x0x7ff76ecab119+117673]
-	GetHandleVerifier [0x0x7ff76ec910a8+11064]
+	GetHandleVerifier [0x0x7ff76fd21eb5+80197]
+	GetHandleVerifier [0x0x7ff76fd21f10+80288]
+	(No symbol) [0x0x7ff76faa02fa]
+	(No symbol) [0x0x7ff76faf7cd7]
+	(No symbol) [0x0x7ff76faf7f9c]
+	(No symbol) [0x0x7ff76fb4ba87]
+	(No symbol) [0x0x7ff76fb203bf]
+	(No symbol) [0x0x7ff76fb487fb]
+	(No symbol) [0x0x7ff76fb20153]
+	(No symbol) [0x0x7ff76fae8b02]
+	(No symbol) [0x0x7ff76fae98d3]
+	GetHandleVerifier [0x0x7ff76ffde83d+2949837]
+	GetHandleVerifier [0x0x7ff76ffd8c6a+2926330]
+	GetHandleVerifier [0x0x7ff76fff86c7+3055959]
+	GetHandleVerifier [0x0x7ff76fd3cfee+191102]
+	GetHandleVerifier [0x0x7ff76fd450af+224063]
+	GetHandleVerifier [0x0x7ff76fd2af64+117236]
+	GetHandleVerifier [0x0x7ff76fd2b119+117673]
+	GetHandleVerifier [0x0x7ff76fd110a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
-	GetHandleVerifier [0x0x7ff76eca1f10+80288]
-	(No symbol) [0x0x7ff76ea202fa]
-	(No symbol) [0x0x7ff76ea77cd7]
-	(No symbol) [0x0x7ff76ea77f9c]
-	(No symbol) [0x0x7ff76eacba87]
-	(No symbol) [0x0x7ff76eaa03bf]
-	(No symbol) [0x0x7ff76eac87fb]
-	(No symbol) [0x0x7ff76eaa0153]
-	(No symbol) [0x0x7ff76ea68b02]
-	(No symbol) [0x0x7ff76ea698d3]
-	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
-	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
-	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
-	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
-	GetHandleVerifier [0x0x7ff76ecc50af+224063]
-	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
-	GetHandleVerifier [0x0x7ff76ecab119+117673]
-	GetHandleVerifier [0x0x7ff76ec910a8+11064]
+	GetHandleVerifier [0x0x7ff76fd21eb5+80197]
+	GetHandleVerifier [0x0x7ff76fd21f10+80288]
+	(No symbol) [0x0x7ff76faa02fa]
+	(No symbol) [0x0x7ff76faf7cd7]
+	(No symbol) [0x0x7ff76faf7f9c]
+	(No symbol) [0x0x7ff76fb4ba87]
+	(No symbol) [0x0x7ff76fb203bf]
+	(No symbol) [0x0x7ff76fb487fb]
+	(No symbol) [0x0x7ff76fb20153]
+	(No symbol) [0x0x7ff76fae8b02]
+	(No symbol) [0x0x7ff76fae98d3]
+	GetHandleVerifier [0x0x7ff76ffde83d+2949837]
+	GetHandleVerifier [0x0x7ff76ffd8c6a+2926330]
+	GetHandleVerifier [0x0x7ff76fff86c7+3055959]
+	GetHandleVerifier [0x0x7ff76fd3cfee+191102]
+	GetHandleVerifier [0x0x7ff76fd450af+224063]
+	GetHandleVerifier [0x0x7ff76fd2af64+117236]
+	GetHandleVerifier [0x0x7ff76fd2b119+117673]
+	GetHandleVerifier [0x0x7ff76fd110a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
-	GetHandleVerifier [0x0x7ff76eca1f10+80288]
-	(No symbol) [0x0x7ff76ea202fa]
-	(No symbol) [0x0x7ff76ea77cd7]
-	(No symbol) [0x0x7ff76ea77f9c]
-	(No symbol) [0x0x7ff76eacba87]
-	(No symbol) [0x0x7ff76eaa03bf]
-	(No symbol) [0x0x7ff76eac87fb]
-	(No symbol) [0x0x7ff76eaa0153]
-	(No symbol) [0x0x7ff76ea68b02]
-	(No symbol) [0x0x7ff76ea698d3]
-	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
-	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
-	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
-	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
-	GetHandleVerifier [0x0x7ff76ecc50af+224063]
-	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
-	GetHandleVerifier [0x0x7ff76ecab119+117673]
-	GetHandleVerifier [0x0x7ff76ec910a8+11064]
+	GetHandleVerifier [0x0x7ff76fd21eb5+80197]
+	GetHandleVerifier [0x0x7ff76fd21f10+80288]
+	(No symbol) [0x0x7ff76faa02fa]
+	(No symbol) [0x0x7ff76faf7cd7]
+	(No symbol) [0x0x7ff76faf7f9c]
+	(No symbol) [0x0x7ff76fb4ba87]
+	(No symbol) [0x0x7ff76fb203bf]
+	(No symbol) [0x0x7ff76fb487fb]
+	(No symbol) [0x0x7ff76fb20153]
+	(No symbol) [0x0x7ff76fae8b02]
+	(No symbol) [0x0x7ff76fae98d3]
+	GetHandleVerifier [0x0x7ff76ffde83d+2949837]
+	GetHandleVerifier [0x0x7ff76ffd8c6a+2926330]
+	GetHandleVerifier [0x0x7ff76fff86c7+3055959]
+	GetHandleVerifier [0x0x7ff76fd3cfee+191102]
+	GetHandleVerifier [0x0x7ff76fd450af+224063]
+	GetHandleVerifier [0x0x7ff76fd2af64+117236]
+	GetHandleVerifier [0x0x7ff76fd2b119+117673]
+	GetHandleVerifier [0x0x7ff76fd110a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
-	GetHandleVerifier [0x0x7ff76eca1f10+80288]
-	(No symbol) [0x0x7ff76ea202fa]
-	(No symbol) [0x0x7ff76ea77cd7]
-	(No symbol) [0x0x7ff76ea77f9c]
-	(No symbol) [0x0x7ff76eacba87]
-	(No symbol) [0x0x7ff76eaa03bf]
-	(No symbol) [0x0x7ff76eac87fb]
-	(No symbol) [0x0x7ff76eaa0153]
-	(No symbol) [0x0x7ff76ea68b02]
-	(No symbol) [0x0x7ff76ea698d3]
-	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
-	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
-	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
-	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
-	GetHandleVerifier [0x0x7ff76ecc50af+224063]
-	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
-	GetHandleVerifier [0x0x7ff76ecab119+117673]
-	GetHandleVerifier [0x0x7ff76ec910a8+11064]
+	GetHandleVerifier [0x0x7ff69d7f1eb5+80197]
+	GetHandleVerifier [0x0x7ff69d7f1f10+80288]
+	(No symbol) [0x0x7ff69d5702fa]
+	(No symbol) [0x0x7ff69d5c7cd7]
+	(No symbol) [0x0x7ff69d5c7f9c]
+	(No symbol) [0x0x7ff69d61ba87]
+	(No symbol) [0x0x7ff69d5f03bf]
+	(No symbol) [0x0x7ff69d6187fb]
+	(No symbol) [0x0x7ff69d5f0153]
+	(No symbol) [0x0x7ff69d5b8b02]
+	(No symbol) [0x0x7ff69d5b98d3]
+	GetHandleVerifier [0x0x7ff69daae83d+2949837]
+	GetHandleVerifier [0x0x7ff69daa8c6a+2926330]
+	GetHandleVerifier [0x0x7ff69dac86c7+3055959]
+	GetHandleVerifier [0x0x7ff69d80cfee+191102]
+	GetHandleVerifier [0x0x7ff69d8150af+224063]
+	GetHandleVerifier [0x0x7ff69d7faf64+117236]
+	GetHandleVerifier [0x0x7ff69d7fb119+117673]
+	GetHandleVerifier [0x0x7ff69d7e10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>£85.44</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
-	GetHandleVerifier [0x0x7ff76eca1f10+80288]
-	(No symbol) [0x0x7ff76ea202fa]
-	(No symbol) [0x0x7ff76ea77cd7]
-	(No symbol) [0x0x7ff76ea77f9c]
-	(No symbol) [0x0x7ff76eacba87]
-	(No symbol) [0x0x7ff76eaa03bf]
-	(No symbol) [0x0x7ff76eac87fb]
-	(No symbol) [0x0x7ff76eaa0153]
-	(No symbol) [0x0x7ff76ea68b02]
-	(No symbol) [0x0x7ff76ea698d3]
-	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
-	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
-	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
-	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
-	GetHandleVerifier [0x0x7ff76ecc50af+224063]
-	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
-	GetHandleVerifier [0x0x7ff76ecab119+117673]
-	GetHandleVerifier [0x0x7ff76ec910a8+11064]
+	GetHandleVerifier [0x0x7ff6ed381eb5+80197]
+	GetHandleVerifier [0x0x7ff6ed381f10+80288]
+	(No symbol) [0x0x7ff6ed1002fa]
+	(No symbol) [0x0x7ff6ed157cd7]
+	(No symbol) [0x0x7ff6ed157f9c]
+	(No symbol) [0x0x7ff6ed1aba87]
+	(No symbol) [0x0x7ff6ed1803bf]
+	(No symbol) [0x0x7ff6ed1a87fb]
+	(No symbol) [0x0x7ff6ed180153]
+	(No symbol) [0x0x7ff6ed148b02]
+	(No symbol) [0x0x7ff6ed1498d3]
+	GetHandleVerifier [0x0x7ff6ed63e83d+2949837]
+	GetHandleVerifier [0x0x7ff6ed638c6a+2926330]
+	GetHandleVerifier [0x0x7ff6ed6586c7+3055959]
+	GetHandleVerifier [0x0x7ff6ed39cfee+191102]
+	GetHandleVerifier [0x0x7ff6ed3a50af+224063]
+	GetHandleVerifier [0x0x7ff6ed38af64+117236]
+	GetHandleVerifier [0x0x7ff6ed38b119+117673]
+	GetHandleVerifier [0x0x7ff6ed3710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
-	GetHandleVerifier [0x0x7ff76eca1f10+80288]
-	(No symbol) [0x0x7ff76ea202fa]
-	(No symbol) [0x0x7ff76ea77cd7]
-	(No symbol) [0x0x7ff76ea77f9c]
-	(No symbol) [0x0x7ff76eacba87]
-	(No symbol) [0x0x7ff76eaa03bf]
-	(No symbol) [0x0x7ff76eac87fb]
-	(No symbol) [0x0x7ff76eaa0153]
-	(No symbol) [0x0x7ff76ea68b02]
-	(No symbol) [0x0x7ff76ea698d3]
-	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
-	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
-	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
-	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
-	GetHandleVerifier [0x0x7ff76ecc50af+224063]
-	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
-	GetHandleVerifier [0x0x7ff76ecab119+117673]
-	GetHandleVerifier [0x0x7ff76ec910a8+11064]
+	GetHandleVerifier [0x0x7ff6e7dc1eb5+80197]
+	GetHandleVerifier [0x0x7ff6e7dc1f10+80288]
+	(No symbol) [0x0x7ff6e7b402fa]
+	(No symbol) [0x0x7ff6e7b97cd7]
+	(No symbol) [0x0x7ff6e7b97f9c]
+	(No symbol) [0x0x7ff6e7beba87]
+	(No symbol) [0x0x7ff6e7bc03bf]
+	(No symbol) [0x0x7ff6e7be87fb]
+	(No symbol) [0x0x7ff6e7bc0153]
+	(No symbol) [0x0x7ff6e7b88b02]
+	(No symbol) [0x0x7ff6e7b898d3]
+	GetHandleVerifier [0x0x7ff6e807e83d+2949837]
+	GetHandleVerifier [0x0x7ff6e8078c6a+2926330]
+	GetHandleVerifier [0x0x7ff6e80986c7+3055959]
+	GetHandleVerifier [0x0x7ff6e7ddcfee+191102]
+	GetHandleVerifier [0x0x7ff6e7de50af+224063]
+	GetHandleVerifier [0x0x7ff6e7dcaf64+117236]
+	GetHandleVerifier [0x0x7ff6e7dcb119+117673]
+	GetHandleVerifier [0x0x7ff6e7db10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff76eca1eb5+80197]
-	GetHandleVerifier [0x0x7ff76eca1f10+80288]
-	(No symbol) [0x0x7ff76ea202fa]
-	(No symbol) [0x0x7ff76ea77cd7]
-	(No symbol) [0x0x7ff76ea77f9c]
-	(No symbol) [0x0x7ff76eacba87]
-	(No symbol) [0x0x7ff76eaa03bf]
-	(No symbol) [0x0x7ff76eac87fb]
-	(No symbol) [0x0x7ff76eaa0153]
-	(No symbol) [0x0x7ff76ea68b02]
-	(No symbol) [0x0x7ff76ea698d3]
-	GetHandleVerifier [0x0x7ff76ef5e83d+2949837]
-	GetHandleVerifier [0x0x7ff76ef58c6a+2926330]
-	GetHandleVerifier [0x0x7ff76ef786c7+3055959]
-	GetHandleVerifier [0x0x7ff76ecbcfee+191102]
-	GetHandleVerifier [0x0x7ff76ecc50af+224063]
-	GetHandleVerifier [0x0x7ff76ecaaf64+117236]
-	GetHandleVerifier [0x0x7ff76ecab119+117673]
-	GetHandleVerifier [0x0x7ff76ec910a8+11064]
+	GetHandleVerifier [0x0x7ff796ca1eb5+80197]
+	GetHandleVerifier [0x0x7ff796ca1f10+80288]
+	(No symbol) [0x0x7ff796a202fa]
+	(No symbol) [0x0x7ff796a77cd7]
+	(No symbol) [0x0x7ff796a77f9c]
+	(No symbol) [0x0x7ff796acba87]
+	(No symbol) [0x0x7ff796aa03bf]
+	(No symbol) [0x0x7ff796ac87fb]
+	(No symbol) [0x0x7ff796aa0153]
+	(No symbol) [0x0x7ff796a68b02]
+	(No symbol) [0x0x7ff796a698d3]
+	GetHandleVerifier [0x0x7ff796f5e83d+2949837]
+	GetHandleVerifier [0x0x7ff796f58c6a+2926330]
+	GetHandleVerifier [0x0x7ff796f786c7+3055959]
+	GetHandleVerifier [0x0x7ff796cbcfee+191102]
+	GetHandleVerifier [0x0x7ff796cc50af+224063]
+	GetHandleVerifier [0x0x7ff796caaf64+117236]
+	GetHandleVerifier [0x0x7ff796cab119+117673]
+	GetHandleVerifier [0x0x7ff796c910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-09-2025.xlsx
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff729c01eb5+80197]
-	GetHandleVerifier [0x0x7ff729c01f10+80288]
-	(No symbol) [0x0x7ff7299802fa]
-	(No symbol) [0x0x7ff7299d7cd7]
-	(No symbol) [0x0x7ff7299d7f9c]
-	(No symbol) [0x0x7ff729a2ba87]
-	(No symbol) [0x0x7ff729a003bf]
-	(No symbol) [0x0x7ff729a287fb]
-	(No symbol) [0x0x7ff729a00153]
-	(No symbol) [0x0x7ff7299c8b02]
-	(No symbol) [0x0x7ff7299c98d3]
-	GetHandleVerifier [0x0x7ff729ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff729eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff729ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff729c1cfee+191102]
-	GetHandleVerifier [0x0x7ff729c250af+224063]
-	GetHandleVerifier [0x0x7ff729c0af64+117236]
-	GetHandleVerifier [0x0x7ff729c0b119+117673]
-	GetHandleVerifier [0x0x7ff729bf10a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77a531eb5+80197]
-	GetHandleVerifier [0x0x7ff77a531f10+80288]
-	(No symbol) [0x0x7ff77a2b02fa]
-	(No symbol) [0x0x7ff77a307cd7]
-	(No symbol) [0x0x7ff77a307f9c]
-	(No symbol) [0x0x7ff77a35ba87]
-	(No symbol) [0x0x7ff77a3303bf]
-	(No symbol) [0x0x7ff77a3587fb]
-	(No symbol) [0x0x7ff77a330153]
-	(No symbol) [0x0x7ff77a2f8b02]
-	(No symbol) [0x0x7ff77a2f98d3]
-	GetHandleVerifier [0x0x7ff77a7ee83d+2949837]
-	GetHandleVerifier [0x0x7ff77a7e8c6a+2926330]
-	GetHandleVerifier [0x0x7ff77a8086c7+3055959]
-	GetHandleVerifier [0x0x7ff77a54cfee+191102]
-	GetHandleVerifier [0x0x7ff77a5550af+224063]
-	GetHandleVerifier [0x0x7ff77a53af64+117236]
-	GetHandleVerifier [0x0x7ff77a53b119+117673]
-	GetHandleVerifier [0x0x7ff77a5210a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff639701eb5+80197]
-	GetHandleVerifier [0x0x7ff639701f10+80288]
-	(No symbol) [0x0x7ff6394802fa]
-	(No symbol) [0x0x7ff6394d7cd7]
-	(No symbol) [0x0x7ff6394d7f9c]
-	(No symbol) [0x0x7ff63952ba87]
-	(No symbol) [0x0x7ff6395003bf]
-	(No symbol) [0x0x7ff6395287fb]
-	(No symbol) [0x0x7ff639500153]
-	(No symbol) [0x0x7ff6394c8b02]
-	(No symbol) [0x0x7ff6394c98d3]
-	GetHandleVerifier [0x0x7ff6399be83d+2949837]
-	GetHandleVerifier [0x0x7ff6399b8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6399d86c7+3055959]
-	GetHandleVerifier [0x0x7ff63971cfee+191102]
-	GetHandleVerifier [0x0x7ff6397250af+224063]
-	GetHandleVerifier [0x0x7ff63970af64+117236]
-	GetHandleVerifier [0x0x7ff63970b119+117673]
-	GetHandleVerifier [0x0x7ff6396f10a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7de8b1eb5+80197]
-	GetHandleVerifier [0x0x7ff7de8b1f10+80288]
-	(No symbol) [0x0x7ff7de6302fa]
-	(No symbol) [0x0x7ff7de687cd7]
-	(No symbol) [0x0x7ff7de687f9c]
-	(No symbol) [0x0x7ff7de6dba87]
-	(No symbol) [0x0x7ff7de6b03bf]
-	(No symbol) [0x0x7ff7de6d87fb]
-	(No symbol) [0x0x7ff7de6b0153]
-	(No symbol) [0x0x7ff7de678b02]
-	(No symbol) [0x0x7ff7de6798d3]
-	GetHandleVerifier [0x0x7ff7deb6e83d+2949837]
-	GetHandleVerifier [0x0x7ff7deb68c6a+2926330]
-	GetHandleVerifier [0x0x7ff7deb886c7+3055959]
-	GetHandleVerifier [0x0x7ff7de8ccfee+191102]
-	GetHandleVerifier [0x0x7ff7de8d50af+224063]
-	GetHandleVerifier [0x0x7ff7de8baf64+117236]
-	GetHandleVerifier [0x0x7ff7de8bb119+117673]
-	GetHandleVerifier [0x0x7ff7de8a10a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff628bc1eb5+80197]
-	GetHandleVerifier [0x0x7ff628bc1f10+80288]
-	(No symbol) [0x0x7ff6289402fa]
-	(No symbol) [0x0x7ff628997cd7]
-	(No symbol) [0x0x7ff628997f9c]
-	(No symbol) [0x0x7ff6289eba87]
-	(No symbol) [0x0x7ff6289c03bf]
-	(No symbol) [0x0x7ff6289e87fb]
-	(No symbol) [0x0x7ff6289c0153]
-	(No symbol) [0x0x7ff628988b02]
-	(No symbol) [0x0x7ff6289898d3]
-	GetHandleVerifier [0x0x7ff628e7e83d+2949837]
-	GetHandleVerifier [0x0x7ff628e78c6a+2926330]
-	GetHandleVerifier [0x0x7ff628e986c7+3055959]
-	GetHandleVerifier [0x0x7ff628bdcfee+191102]
-	GetHandleVerifier [0x0x7ff628be50af+224063]
-	GetHandleVerifier [0x0x7ff628bcaf64+117236]
-	GetHandleVerifier [0x0x7ff628bcb119+117673]
-	GetHandleVerifier [0x0x7ff628bb10a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff792391eb5+80197]
-	GetHandleVerifier [0x0x7ff792391f10+80288]
-	(No symbol) [0x0x7ff7921102fa]
-	(No symbol) [0x0x7ff792167cd7]
-	(No symbol) [0x0x7ff792167f9c]
-	(No symbol) [0x0x7ff7921bba87]
-	(No symbol) [0x0x7ff7921903bf]
-	(No symbol) [0x0x7ff7921b87fb]
-	(No symbol) [0x0x7ff792190153]
-	(No symbol) [0x0x7ff792158b02]
-	(No symbol) [0x0x7ff7921598d3]
-	GetHandleVerifier [0x0x7ff79264e83d+2949837]
-	GetHandleVerifier [0x0x7ff792648c6a+2926330]
-	GetHandleVerifier [0x0x7ff7926686c7+3055959]
-	GetHandleVerifier [0x0x7ff7923acfee+191102]
-	GetHandleVerifier [0x0x7ff7923b50af+224063]
-	GetHandleVerifier [0x0x7ff79239af64+117236]
-	GetHandleVerifier [0x0x7ff79239b119+117673]
-	GetHandleVerifier [0x0x7ff7923810a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6b6c91eb5+80197]
-	GetHandleVerifier [0x0x7ff6b6c91f10+80288]
-	(No symbol) [0x0x7ff6b6a102fa]
-	(No symbol) [0x0x7ff6b6a67cd7]
-	(No symbol) [0x0x7ff6b6a67f9c]
-	(No symbol) [0x0x7ff6b6abba87]
-	(No symbol) [0x0x7ff6b6a903bf]
-	(No symbol) [0x0x7ff6b6ab87fb]
-	(No symbol) [0x0x7ff6b6a90153]
-	(No symbol) [0x0x7ff6b6a58b02]
-	(No symbol) [0x0x7ff6b6a598d3]
-	GetHandleVerifier [0x0x7ff6b6f4e83d+2949837]
-	GetHandleVerifier [0x0x7ff6b6f48c6a+2926330]
-	GetHandleVerifier [0x0x7ff6b6f686c7+3055959]
-	GetHandleVerifier [0x0x7ff6b6cacfee+191102]
-	GetHandleVerifier [0x0x7ff6b6cb50af+224063]
-	GetHandleVerifier [0x0x7ff6b6c9af64+117236]
-	GetHandleVerifier [0x0x7ff6b6c9b119+117673]
-	GetHandleVerifier [0x0x7ff6b6c810a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff623691eb5+80197]
-	GetHandleVerifier [0x0x7ff623691f10+80288]
-	(No symbol) [0x0x7ff6234102fa]
-	(No symbol) [0x0x7ff623467cd7]
-	(No symbol) [0x0x7ff623467f9c]
-	(No symbol) [0x0x7ff6234bba87]
-	(No symbol) [0x0x7ff6234903bf]
-	(No symbol) [0x0x7ff6234b87fb]
-	(No symbol) [0x0x7ff623490153]
-	(No symbol) [0x0x7ff623458b02]
-	(No symbol) [0x0x7ff6234598d3]
-	GetHandleVerifier [0x0x7ff62394e83d+2949837]
-	GetHandleVerifier [0x0x7ff623948c6a+2926330]
-	GetHandleVerifier [0x0x7ff6239686c7+3055959]
-	GetHandleVerifier [0x0x7ff6236acfee+191102]
-	GetHandleVerifier [0x0x7ff6236b50af+224063]
-	GetHandleVerifier [0x0x7ff62369af64+117236]
-	GetHandleVerifier [0x0x7ff62369b119+117673]
-	GetHandleVerifier [0x0x7ff6236810a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff65ebb1eb5+80197]
-	GetHandleVerifier [0x0x7ff65ebb1f10+80288]
-	(No symbol) [0x0x7ff65e9302fa]
-	(No symbol) [0x0x7ff65e987cd7]
-	(No symbol) [0x0x7ff65e987f9c]
-	(No symbol) [0x0x7ff65e9dba87]
-	(No symbol) [0x0x7ff65e9b03bf]
-	(No symbol) [0x0x7ff65e9d87fb]
-	(No symbol) [0x0x7ff65e9b0153]
-	(No symbol) [0x0x7ff65e978b02]
-	(No symbol) [0x0x7ff65e9798d3]
-	GetHandleVerifier [0x0x7ff65ee6e83d+2949837]
-	GetHandleVerifier [0x0x7ff65ee68c6a+2926330]
-	GetHandleVerifier [0x0x7ff65ee886c7+3055959]
-	GetHandleVerifier [0x0x7ff65ebccfee+191102]
-	GetHandleVerifier [0x0x7ff65ebd50af+224063]
-	GetHandleVerifier [0x0x7ff65ebbaf64+117236]
-	GetHandleVerifier [0x0x7ff65ebbb119+117673]
-	GetHandleVerifier [0x0x7ff65eba10a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff65ebb1eb5+80197]
-	GetHandleVerifier [0x0x7ff65ebb1f10+80288]
-	(No symbol) [0x0x7ff65e9302fa]
-	(No symbol) [0x0x7ff65e987cd7]
-	(No symbol) [0x0x7ff65e987f9c]
-	(No symbol) [0x0x7ff65e9dba87]
-	(No symbol) [0x0x7ff65e9b03bf]
-	(No symbol) [0x0x7ff65e9d87fb]
-	(No symbol) [0x0x7ff65e9b0153]
-	(No symbol) [0x0x7ff65e978b02]
-	(No symbol) [0x0x7ff65e9798d3]
-	GetHandleVerifier [0x0x7ff65ee6e83d+2949837]
-	GetHandleVerifier [0x0x7ff65ee68c6a+2926330]
-	GetHandleVerifier [0x0x7ff65ee886c7+3055959]
-	GetHandleVerifier [0x0x7ff65ebccfee+191102]
-	GetHandleVerifier [0x0x7ff65ebd50af+224063]
-	GetHandleVerifier [0x0x7ff65ebbaf64+117236]
-	GetHandleVerifier [0x0x7ff65ebbb119+117673]
-	GetHandleVerifier [0x0x7ff65eba10a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff65ebb1eb5+80197]
-	GetHandleVerifier [0x0x7ff65ebb1f10+80288]
-	(No symbol) [0x0x7ff65e9302fa]
-	(No symbol) [0x0x7ff65e987cd7]
-	(No symbol) [0x0x7ff65e987f9c]
-	(No symbol) [0x0x7ff65e9dba87]
-	(No symbol) [0x0x7ff65e9b03bf]
-	(No symbol) [0x0x7ff65e9d87fb]
-	(No symbol) [0x0x7ff65e9b0153]
-	(No symbol) [0x0x7ff65e978b02]
-	(No symbol) [0x0x7ff65e9798d3]
-	GetHandleVerifier [0x0x7ff65ee6e83d+2949837]
-	GetHandleVerifier [0x0x7ff65ee68c6a+2926330]
-	GetHandleVerifier [0x0x7ff65ee886c7+3055959]
-	GetHandleVerifier [0x0x7ff65ebccfee+191102]
-	GetHandleVerifier [0x0x7ff65ebd50af+224063]
-	GetHandleVerifier [0x0x7ff65ebbaf64+117236]
-	GetHandleVerifier [0x0x7ff65ebbb119+117673]
-	GetHandleVerifier [0x0x7ff65eba10a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff65ebb1eb5+80197]
-	GetHandleVerifier [0x0x7ff65ebb1f10+80288]
-	(No symbol) [0x0x7ff65e9302fa]
-	(No symbol) [0x0x7ff65e987cd7]
-	(No symbol) [0x0x7ff65e987f9c]
-	(No symbol) [0x0x7ff65e9dba87]
-	(No symbol) [0x0x7ff65e9b03bf]
-	(No symbol) [0x0x7ff65e9d87fb]
-	(No symbol) [0x0x7ff65e9b0153]
-	(No symbol) [0x0x7ff65e978b02]
-	(No symbol) [0x0x7ff65e9798d3]
-	GetHandleVerifier [0x0x7ff65ee6e83d+2949837]
-	GetHandleVerifier [0x0x7ff65ee68c6a+2926330]
-	GetHandleVerifier [0x0x7ff65ee886c7+3055959]
-	GetHandleVerifier [0x0x7ff65ebccfee+191102]
-	GetHandleVerifier [0x0x7ff65ebd50af+224063]
-	GetHandleVerifier [0x0x7ff65ebbaf64+117236]
-	GetHandleVerifier [0x0x7ff65ebbb119+117673]
-	GetHandleVerifier [0x0x7ff65eba10a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff65e681eb5+80197]
-	GetHandleVerifier [0x0x7ff65e681f10+80288]
-	(No symbol) [0x0x7ff65e4002fa]
-	(No symbol) [0x0x7ff65e457cd7]
-	(No symbol) [0x0x7ff65e457f9c]
-	(No symbol) [0x0x7ff65e4aba87]
-	(No symbol) [0x0x7ff65e4803bf]
-	(No symbol) [0x0x7ff65e4a87fb]
-	(No symbol) [0x0x7ff65e480153]
-	(No symbol) [0x0x7ff65e448b02]
-	(No symbol) [0x0x7ff65e4498d3]
-	GetHandleVerifier [0x0x7ff65e93e83d+2949837]
-	GetHandleVerifier [0x0x7ff65e938c6a+2926330]
-	GetHandleVerifier [0x0x7ff65e9586c7+3055959]
-	GetHandleVerifier [0x0x7ff65e69cfee+191102]
-	GetHandleVerifier [0x0x7ff65e6a50af+224063]
-	GetHandleVerifier [0x0x7ff65e68af64+117236]
-	GetHandleVerifier [0x0x7ff65e68b119+117673]
-	GetHandleVerifier [0x0x7ff65e6710a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff65e681eb5+80197]
-	GetHandleVerifier [0x0x7ff65e681f10+80288]
-	(No symbol) [0x0x7ff65e4002fa]
-	(No symbol) [0x0x7ff65e457cd7]
-	(No symbol) [0x0x7ff65e457f9c]
-	(No symbol) [0x0x7ff65e4aba87]
-	(No symbol) [0x0x7ff65e4803bf]
-	(No symbol) [0x0x7ff65e4a87fb]
-	(No symbol) [0x0x7ff65e480153]
-	(No symbol) [0x0x7ff65e448b02]
-	(No symbol) [0x0x7ff65e4498d3]
-	GetHandleVerifier [0x0x7ff65e93e83d+2949837]
-	GetHandleVerifier [0x0x7ff65e938c6a+2926330]
-	GetHandleVerifier [0x0x7ff65e9586c7+3055959]
-	GetHandleVerifier [0x0x7ff65e69cfee+191102]
-	GetHandleVerifier [0x0x7ff65e6a50af+224063]
-	GetHandleVerifier [0x0x7ff65e68af64+117236]
-	GetHandleVerifier [0x0x7ff65e68b119+117673]
-	GetHandleVerifier [0x0x7ff65e6710a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff65e681eb5+80197]
-	GetHandleVerifier [0x0x7ff65e681f10+80288]
-	(No symbol) [0x0x7ff65e4002fa]
-	(No symbol) [0x0x7ff65e457cd7]
-	(No symbol) [0x0x7ff65e457f9c]
-	(No symbol) [0x0x7ff65e4aba87]
-	(No symbol) [0x0x7ff65e4803bf]
-	(No symbol) [0x0x7ff65e4a87fb]
-	(No symbol) [0x0x7ff65e480153]
-	(No symbol) [0x0x7ff65e448b02]
-	(No symbol) [0x0x7ff65e4498d3]
-	GetHandleVerifier [0x0x7ff65e93e83d+2949837]
-	GetHandleVerifier [0x0x7ff65e938c6a+2926330]
-	GetHandleVerifier [0x0x7ff65e9586c7+3055959]
-	GetHandleVerifier [0x0x7ff65e69cfee+191102]
-	GetHandleVerifier [0x0x7ff65e6a50af+224063]
-	GetHandleVerifier [0x0x7ff65e68af64+117236]
-	GetHandleVerifier [0x0x7ff65e68b119+117673]
-	GetHandleVerifier [0x0x7ff65e6710a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff65e681eb5+80197]
-	GetHandleVerifier [0x0x7ff65e681f10+80288]
-	(No symbol) [0x0x7ff65e4002fa]
-	(No symbol) [0x0x7ff65e457cd7]
-	(No symbol) [0x0x7ff65e457f9c]
-	(No symbol) [0x0x7ff65e4aba87]
-	(No symbol) [0x0x7ff65e4803bf]
-	(No symbol) [0x0x7ff65e4a87fb]
-	(No symbol) [0x0x7ff65e480153]
-	(No symbol) [0x0x7ff65e448b02]
-	(No symbol) [0x0x7ff65e4498d3]
-	GetHandleVerifier [0x0x7ff65e93e83d+2949837]
-	GetHandleVerifier [0x0x7ff65e938c6a+2926330]
-	GetHandleVerifier [0x0x7ff65e9586c7+3055959]
-	GetHandleVerifier [0x0x7ff65e69cfee+191102]
-	GetHandleVerifier [0x0x7ff65e6a50af+224063]
-	GetHandleVerifier [0x0x7ff65e68af64+117236]
-	GetHandleVerifier [0x0x7ff65e68b119+117673]
-	GetHandleVerifier [0x0x7ff65e6710a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff65e681eb5+80197]
-	GetHandleVerifier [0x0x7ff65e681f10+80288]
-	(No symbol) [0x0x7ff65e4002fa]
-	(No symbol) [0x0x7ff65e457cd7]
-	(No symbol) [0x0x7ff65e457f9c]
-	(No symbol) [0x0x7ff65e4aba87]
-	(No symbol) [0x0x7ff65e4803bf]
-	(No symbol) [0x0x7ff65e4a87fb]
-	(No symbol) [0x0x7ff65e480153]
-	(No symbol) [0x0x7ff65e448b02]
-	(No symbol) [0x0x7ff65e4498d3]
-	GetHandleVerifier [0x0x7ff65e93e83d+2949837]
-	GetHandleVerifier [0x0x7ff65e938c6a+2926330]
-	GetHandleVerifier [0x0x7ff65e9586c7+3055959]
-	GetHandleVerifier [0x0x7ff65e69cfee+191102]
-	GetHandleVerifier [0x0x7ff65e6a50af+224063]
-	GetHandleVerifier [0x0x7ff65e68af64+117236]
-	GetHandleVerifier [0x0x7ff65e68b119+117673]
-	GetHandleVerifier [0x0x7ff65e6710a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff76fd21eb5+80197]
-	GetHandleVerifier [0x0x7ff76fd21f10+80288]
-	(No symbol) [0x0x7ff76faa02fa]
-	(No symbol) [0x0x7ff76faf7cd7]
-	(No symbol) [0x0x7ff76faf7f9c]
-	(No symbol) [0x0x7ff76fb4ba87]
-	(No symbol) [0x0x7ff76fb203bf]
-	(No symbol) [0x0x7ff76fb487fb]
-	(No symbol) [0x0x7ff76fb20153]
-	(No symbol) [0x0x7ff76fae8b02]
-	(No symbol) [0x0x7ff76fae98d3]
-	GetHandleVerifier [0x0x7ff76ffde83d+2949837]
-	GetHandleVerifier [0x0x7ff76ffd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff76fff86c7+3055959]
-	GetHandleVerifier [0x0x7ff76fd3cfee+191102]
-	GetHandleVerifier [0x0x7ff76fd450af+224063]
-	GetHandleVerifier [0x0x7ff76fd2af64+117236]
-	GetHandleVerifier [0x0x7ff76fd2b119+117673]
-	GetHandleVerifier [0x0x7ff76fd110a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff76fd21eb5+80197]
-	GetHandleVerifier [0x0x7ff76fd21f10+80288]
-	(No symbol) [0x0x7ff76faa02fa]
-	(No symbol) [0x0x7ff76faf7cd7]
-	(No symbol) [0x0x7ff76faf7f9c]
-	(No symbol) [0x0x7ff76fb4ba87]
-	(No symbol) [0x0x7ff76fb203bf]
-	(No symbol) [0x0x7ff76fb487fb]
-	(No symbol) [0x0x7ff76fb20153]
-	(No symbol) [0x0x7ff76fae8b02]
-	(No symbol) [0x0x7ff76fae98d3]
-	GetHandleVerifier [0x0x7ff76ffde83d+2949837]
-	GetHandleVerifier [0x0x7ff76ffd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff76fff86c7+3055959]
-	GetHandleVerifier [0x0x7ff76fd3cfee+191102]
-	GetHandleVerifier [0x0x7ff76fd450af+224063]
-	GetHandleVerifier [0x0x7ff76fd2af64+117236]
-	GetHandleVerifier [0x0x7ff76fd2b119+117673]
-	GetHandleVerifier [0x0x7ff76fd110a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff76fd21eb5+80197]
-	GetHandleVerifier [0x0x7ff76fd21f10+80288]
-	(No symbol) [0x0x7ff76faa02fa]
-	(No symbol) [0x0x7ff76faf7cd7]
-	(No symbol) [0x0x7ff76faf7f9c]
-	(No symbol) [0x0x7ff76fb4ba87]
-	(No symbol) [0x0x7ff76fb203bf]
-	(No symbol) [0x0x7ff76fb487fb]
-	(No symbol) [0x0x7ff76fb20153]
-	(No symbol) [0x0x7ff76fae8b02]
-	(No symbol) [0x0x7ff76fae98d3]
-	GetHandleVerifier [0x0x7ff76ffde83d+2949837]
-	GetHandleVerifier [0x0x7ff76ffd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff76fff86c7+3055959]
-	GetHandleVerifier [0x0x7ff76fd3cfee+191102]
-	GetHandleVerifier [0x0x7ff76fd450af+224063]
-	GetHandleVerifier [0x0x7ff76fd2af64+117236]
-	GetHandleVerifier [0x0x7ff76fd2b119+117673]
-	GetHandleVerifier [0x0x7ff76fd110a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>£43.63</t>
+          <t>£43.80</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff69d7f1eb5+80197]
-	GetHandleVerifier [0x0x7ff69d7f1f10+80288]
-	(No symbol) [0x0x7ff69d5702fa]
-	(No symbol) [0x0x7ff69d5c7cd7]
-	(No symbol) [0x0x7ff69d5c7f9c]
-	(No symbol) [0x0x7ff69d61ba87]
-	(No symbol) [0x0x7ff69d5f03bf]
-	(No symbol) [0x0x7ff69d6187fb]
-	(No symbol) [0x0x7ff69d5f0153]
-	(No symbol) [0x0x7ff69d5b8b02]
-	(No symbol) [0x0x7ff69d5b98d3]
-	GetHandleVerifier [0x0x7ff69daae83d+2949837]
-	GetHandleVerifier [0x0x7ff69daa8c6a+2926330]
-	GetHandleVerifier [0x0x7ff69dac86c7+3055959]
-	GetHandleVerifier [0x0x7ff69d80cfee+191102]
-	GetHandleVerifier [0x0x7ff69d8150af+224063]
-	GetHandleVerifier [0x0x7ff69d7faf64+117236]
-	GetHandleVerifier [0x0x7ff69d7fb119+117673]
-	GetHandleVerifier [0x0x7ff69d7e10a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3222,12 +3222,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>£43.63</t>
+          <t>£43.30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£85.44</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6ed381eb5+80197]
-	GetHandleVerifier [0x0x7ff6ed381f10+80288]
-	(No symbol) [0x0x7ff6ed1002fa]
-	(No symbol) [0x0x7ff6ed157cd7]
-	(No symbol) [0x0x7ff6ed157f9c]
-	(No symbol) [0x0x7ff6ed1aba87]
-	(No symbol) [0x0x7ff6ed1803bf]
-	(No symbol) [0x0x7ff6ed1a87fb]
-	(No symbol) [0x0x7ff6ed180153]
-	(No symbol) [0x0x7ff6ed148b02]
-	(No symbol) [0x0x7ff6ed1498d3]
-	GetHandleVerifier [0x0x7ff6ed63e83d+2949837]
-	GetHandleVerifier [0x0x7ff6ed638c6a+2926330]
-	GetHandleVerifier [0x0x7ff6ed6586c7+3055959]
-	GetHandleVerifier [0x0x7ff6ed39cfee+191102]
-	GetHandleVerifier [0x0x7ff6ed3a50af+224063]
-	GetHandleVerifier [0x0x7ff6ed38af64+117236]
-	GetHandleVerifier [0x0x7ff6ed38b119+117673]
-	GetHandleVerifier [0x0x7ff6ed3710a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6e7dc1eb5+80197]
-	GetHandleVerifier [0x0x7ff6e7dc1f10+80288]
-	(No symbol) [0x0x7ff6e7b402fa]
-	(No symbol) [0x0x7ff6e7b97cd7]
-	(No symbol) [0x0x7ff6e7b97f9c]
-	(No symbol) [0x0x7ff6e7beba87]
-	(No symbol) [0x0x7ff6e7bc03bf]
-	(No symbol) [0x0x7ff6e7be87fb]
-	(No symbol) [0x0x7ff6e7bc0153]
-	(No symbol) [0x0x7ff6e7b88b02]
-	(No symbol) [0x0x7ff6e7b898d3]
-	GetHandleVerifier [0x0x7ff6e807e83d+2949837]
-	GetHandleVerifier [0x0x7ff6e8078c6a+2926330]
-	GetHandleVerifier [0x0x7ff6e80986c7+3055959]
-	GetHandleVerifier [0x0x7ff6e7ddcfee+191102]
-	GetHandleVerifier [0x0x7ff6e7de50af+224063]
-	GetHandleVerifier [0x0x7ff6e7dcaf64+117236]
-	GetHandleVerifier [0x0x7ff6e7dcb119+117673]
-	GetHandleVerifier [0x0x7ff6e7db10a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>£44.38</t>
+          <t>£43.14</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff796ca1eb5+80197]
-	GetHandleVerifier [0x0x7ff796ca1f10+80288]
-	(No symbol) [0x0x7ff796a202fa]
-	(No symbol) [0x0x7ff796a77cd7]
-	(No symbol) [0x0x7ff796a77f9c]
-	(No symbol) [0x0x7ff796acba87]
-	(No symbol) [0x0x7ff796aa03bf]
-	(No symbol) [0x0x7ff796ac87fb]
-	(No symbol) [0x0x7ff796aa0153]
-	(No symbol) [0x0x7ff796a68b02]
-	(No symbol) [0x0x7ff796a698d3]
-	GetHandleVerifier [0x0x7ff796f5e83d+2949837]
-	GetHandleVerifier [0x0x7ff796f58c6a+2926330]
-	GetHandleVerifier [0x0x7ff796f786c7+3055959]
-	GetHandleVerifier [0x0x7ff796cbcfee+191102]
-	GetHandleVerifier [0x0x7ff796cc50af+224063]
-	GetHandleVerifier [0x0x7ff796caaf64+117236]
-	GetHandleVerifier [0x0x7ff796cab119+117673]
-	GetHandleVerifier [0x0x7ff796c910a8+11064]
+	GetHandleVerifier [0x0x7ff705331eb5+80197]
+	GetHandleVerifier [0x0x7ff705331f10+80288]
+	(No symbol) [0x0x7ff7050b02fa]
+	(No symbol) [0x0x7ff705107cd7]
+	(No symbol) [0x0x7ff705107f9c]
+	(No symbol) [0x0x7ff70515ba87]
+	(No symbol) [0x0x7ff7051303bf]
+	(No symbol) [0x0x7ff7051587fb]
+	(No symbol) [0x0x7ff705130153]
+	(No symbol) [0x0x7ff7050f8b02]
+	(No symbol) [0x0x7ff7050f98d3]
+	GetHandleVerifier [0x0x7ff7055ee83d+2949837]
+	GetHandleVerifier [0x0x7ff7055e8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7056086c7+3055959]
+	GetHandleVerifier [0x0x7ff70534cfee+191102]
+	GetHandleVerifier [0x0x7ff7053550af+224063]
+	GetHandleVerifier [0x0x7ff70533af64+117236]
+	GetHandleVerifier [0x0x7ff70533b119+117673]
+	GetHandleVerifier [0x0x7ff7053210a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
